--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E6869B-7B44-4147-A0C1-566AB301F33D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C01372F-3DF2-4A9E-A197-F8E5DD290680}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C01372F-3DF2-4A9E-A197-F8E5DD290680}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B9BC24-E82C-4FCB-B496-C31D3E160B86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -1000,7 +1000,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1060,8 +1060,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1083,6 +1091,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2300,7 +2314,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2926,6 +2940,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -6369,23 +6389,31 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>35</v>
+      </c>
+      <c r="D8" s="111">
+        <v>7</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
-      <c r="H8" s="73"/>
+      <c r="H8" s="73">
+        <v>22</v>
+      </c>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
+      <c r="M8" s="112">
+        <v>22</v>
+      </c>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
       <c r="P8" s="112"/>
@@ -6396,7 +6424,7 @@
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T8" s="41"/>
       <c r="U8" s="107">
@@ -6409,7 +6437,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -6444,7 +6472,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>98</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -6452,7 +6482,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -6484,7 +6514,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -6519,30 +6549,38 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>152</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>3</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -6551,15 +6589,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3576</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -6594,7 +6632,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>35</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -6602,7 +6642,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -6634,7 +6674,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -6669,19 +6709,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -6709,7 +6753,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -6744,47 +6788,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3180</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>19</v>
+      </c>
+      <c r="H13" s="79">
+        <v>24</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3161</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>3</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>10</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>75840</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -6826,19 +6886,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>3</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -6866,7 +6930,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -6901,7 +6965,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -6909,7 +6975,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -6941,7 +7007,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -6976,7 +7042,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>1</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -6984,7 +7052,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -7016,7 +7084,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -7126,7 +7194,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -7134,7 +7204,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -7166,7 +7236,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -7276,19 +7346,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -7316,7 +7390,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -7351,7 +7425,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>6</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -7359,7 +7435,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -7391,7 +7467,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -7426,7 +7502,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>3</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -7434,7 +7512,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -7466,7 +7544,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -7501,19 +7579,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>1</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -7541,7 +7623,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -7583,19 +7665,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -7623,7 +7709,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -7665,7 +7751,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>9</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -7673,7 +7761,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -7705,7 +7793,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -7740,30 +7828,40 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>152</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>3</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
+      <c r="N26" s="112">
+        <v>1</v>
+      </c>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -7772,15 +7870,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3577</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -7855,7 +7953,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -7863,7 +7963,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -7895,7 +7995,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -7914,30 +8014,40 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>124</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>14</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>10</v>
+      </c>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>3</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -7946,15 +8056,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2640</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -7973,19 +8083,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>63</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -8013,7 +8127,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -8025,7 +8139,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -8033,7 +8149,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -8065,7 +8181,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -8129,7 +8245,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>6</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -8137,7 +8255,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -8169,7 +8287,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -8181,7 +8299,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -8189,7 +8309,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -8221,7 +8341,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -8233,30 +8353,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>90</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>11</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>10</v>
+      </c>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -8265,15 +8395,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1910</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -8337,7 +8467,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>1</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -8345,7 +8477,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -8377,7 +8509,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -8389,47 +8521,63 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4609</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="79"/>
+      <c r="G38" s="78">
+        <v>78</v>
+      </c>
+      <c r="H38" s="79">
+        <v>1</v>
+      </c>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4531</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
-      <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="L38" s="121">
+        <v>13</v>
+      </c>
+      <c r="M38" s="121">
+        <v>1</v>
+      </c>
+      <c r="N38" s="121">
+        <v>40</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>25</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>27187</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -8545,19 +8693,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>95</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -8585,7 +8737,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2288</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -8597,30 +8749,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>289</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>22</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>10</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>6</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>6</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -8629,15 +8791,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>3204</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -8692,30 +8854,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>40125</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1152</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>38973</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>570</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>275</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>307</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -8724,15 +8898,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>6912</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>233841</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -8788,7 +8962,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>1</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -8796,7 +8972,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="4"/>
@@ -8828,7 +9004,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -8892,19 +9068,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2810</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2810</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -8932,7 +9112,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16861</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -8944,7 +9124,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -8952,7 +9134,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -8984,7 +9166,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -8996,7 +9178,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>2</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -9004,7 +9188,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -9036,7 +9220,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -9100,7 +9284,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -9108,7 +9294,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -9140,7 +9326,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -9152,7 +9338,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>1</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -9160,7 +9348,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -9192,7 +9380,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -9204,7 +9392,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>10</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -9212,7 +9402,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -9244,7 +9434,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -9459,11 +9649,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>52013</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -9472,40 +9662,40 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1302</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>50711</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
@@ -9513,24 +9703,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1302</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>8844</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1302</v>
+      </c>
+      <c r="W60" s="209">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>379667</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -10272,30 +10462,40 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>34</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>11</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
-      <c r="L8" s="112"/>
+      <c r="L8" s="112">
+        <v>1</v>
+      </c>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
+      <c r="P8" s="112">
+        <v>10</v>
+      </c>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -10304,15 +10504,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -10347,7 +10547,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>98</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -10355,7 +10557,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -10387,7 +10589,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -10422,15 +10624,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>149</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>5</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -10441,11 +10647,13 @@
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>5</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -10454,15 +10662,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -10497,15 +10705,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>35</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>2</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -10516,11 +10728,13 @@
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>2</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -10529,15 +10743,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -10572,30 +10786,38 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
-      <c r="G12" s="76"/>
+      <c r="G12" s="76">
+        <v>5</v>
+      </c>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
       <c r="M12" s="112"/>
       <c r="N12" s="112"/>
       <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
+      <c r="P12" s="112">
+        <v>5</v>
+      </c>
       <c r="Q12" s="120"/>
       <c r="R12" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S12" s="124">
         <f t="shared" si="1"/>
@@ -10604,15 +10826,15 @@
       <c r="T12" s="41"/>
       <c r="U12" s="107">
         <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V12" s="130">
         <f t="shared" ref="V12:V41" si="6">U12/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -10647,47 +10869,59 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3160</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>14</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3146</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>13</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="P13" s="121">
+        <v>1</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>75492</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -10729,30 +10963,38 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>3</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
-      <c r="G14" s="76"/>
+      <c r="G14" s="76">
+        <v>1</v>
+      </c>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
       <c r="M14" s="112"/>
       <c r="N14" s="112"/>
       <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
+      <c r="P14" s="112">
+        <v>1</v>
+      </c>
       <c r="Q14" s="120"/>
       <c r="R14" s="96">
         <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="126">
         <f t="shared" si="7"/>
@@ -10761,15 +11003,15 @@
       <c r="T14" s="41"/>
       <c r="U14" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V14" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -10804,7 +11046,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -10812,7 +11056,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -10844,7 +11088,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -10879,11 +11123,15 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>1</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="76">
+        <v>1</v>
+      </c>
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
@@ -10898,11 +11146,13 @@
       <c r="M16" s="112"/>
       <c r="N16" s="112"/>
       <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
+      <c r="P16" s="112">
+        <v>1</v>
+      </c>
       <c r="Q16" s="120"/>
       <c r="R16" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="124">
         <f t="shared" si="7"/>
@@ -10911,11 +11161,11 @@
       <c r="T16" s="41"/>
       <c r="U16" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V16" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
@@ -11029,7 +11279,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -11037,7 +11289,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -11069,7 +11321,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -11179,30 +11431,38 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
-      <c r="G20" s="76"/>
+      <c r="G20" s="76">
+        <v>1</v>
+      </c>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
       <c r="M20" s="112"/>
       <c r="N20" s="112"/>
       <c r="O20" s="112"/>
-      <c r="P20" s="112"/>
+      <c r="P20" s="112">
+        <v>1</v>
+      </c>
       <c r="Q20" s="120"/>
       <c r="R20" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="124">
         <f t="shared" si="7"/>
@@ -11211,15 +11471,15 @@
       <c r="T20" s="41"/>
       <c r="U20" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V20" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -11254,15 +11514,19 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>6</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
-      <c r="G21" s="76"/>
+      <c r="G21" s="76">
+        <v>1</v>
+      </c>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -11273,11 +11537,13 @@
       <c r="M21" s="112"/>
       <c r="N21" s="112"/>
       <c r="O21" s="112"/>
-      <c r="P21" s="112"/>
+      <c r="P21" s="112">
+        <v>1</v>
+      </c>
       <c r="Q21" s="120"/>
       <c r="R21" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="124">
         <f t="shared" si="7"/>
@@ -11286,15 +11552,15 @@
       <c r="T21" s="41"/>
       <c r="U21" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V21" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -11329,15 +11595,19 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>3</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
-      <c r="G22" s="76"/>
+      <c r="G22" s="76">
+        <v>1</v>
+      </c>
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -11348,11 +11618,13 @@
       <c r="M22" s="112"/>
       <c r="N22" s="112"/>
       <c r="O22" s="112"/>
-      <c r="P22" s="112"/>
+      <c r="P22" s="112">
+        <v>1</v>
+      </c>
       <c r="Q22" s="120"/>
       <c r="R22" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="124">
         <f t="shared" si="7"/>
@@ -11361,15 +11633,15 @@
       <c r="T22" s="41"/>
       <c r="U22" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V22" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -11404,11 +11676,17 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>1</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
-      <c r="G23" s="76"/>
+      <c r="G23" s="76">
+        <v>1</v>
+      </c>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
@@ -11416,18 +11694,20 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
       <c r="M23" s="112"/>
       <c r="N23" s="112"/>
       <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
+      <c r="P23" s="112">
+        <v>1</v>
+      </c>
       <c r="Q23" s="120"/>
       <c r="R23" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="124">
         <f t="shared" si="7"/>
@@ -11436,15 +11716,15 @@
       <c r="T23" s="42"/>
       <c r="U23" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V23" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -11486,19 +11766,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -11526,7 +11810,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -11568,15 +11852,19 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>9</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
-      <c r="G25" s="76"/>
+      <c r="G25" s="76">
+        <v>1</v>
+      </c>
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -11587,11 +11875,13 @@
       <c r="M25" s="112"/>
       <c r="N25" s="112"/>
       <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
+      <c r="P25" s="112">
+        <v>1</v>
+      </c>
       <c r="Q25" s="120"/>
       <c r="R25" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="124">
         <f t="shared" si="7"/>
@@ -11600,15 +11890,15 @@
       <c r="T25" s="41"/>
       <c r="U25" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V25" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -11643,19 +11933,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>149</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -11683,7 +11977,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3577</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -11758,11 +12052,15 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
-      <c r="G28" s="76"/>
+      <c r="G28" s="76">
+        <v>2</v>
+      </c>
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
@@ -11777,11 +12075,13 @@
       <c r="M28" s="112"/>
       <c r="N28" s="112"/>
       <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
+      <c r="P28" s="112">
+        <v>2</v>
+      </c>
       <c r="Q28" s="120"/>
       <c r="R28" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28" s="124">
         <f t="shared" si="7"/>
@@ -11790,11 +12090,11 @@
       <c r="T28" s="42"/>
       <c r="U28" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V28" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
@@ -11817,15 +12117,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>110</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>10</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -11836,11 +12140,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>10</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -11849,15 +12155,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -11876,30 +12182,38 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>63</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>10</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
+      <c r="P30" s="112">
+        <v>10</v>
+      </c>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="7"/>
@@ -11908,15 +12222,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -11928,15 +12242,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>15</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>2</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -11947,11 +12265,13 @@
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
+      <c r="P31" s="112">
+        <v>2</v>
+      </c>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="7"/>
@@ -11960,15 +12280,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -12032,15 +12352,19 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>6</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
-      <c r="G33" s="76"/>
+      <c r="G33" s="76">
+        <v>2</v>
+      </c>
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -12051,11 +12375,13 @@
       <c r="M33" s="112"/>
       <c r="N33" s="112"/>
       <c r="O33" s="112"/>
-      <c r="P33" s="112"/>
+      <c r="P33" s="112">
+        <v>2</v>
+      </c>
       <c r="Q33" s="120"/>
       <c r="R33" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S33" s="124">
         <f t="shared" si="7"/>
@@ -12064,15 +12390,15 @@
       <c r="T33" s="41"/>
       <c r="U33" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -12084,11 +12410,15 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>2</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
-      <c r="G34" s="76"/>
+      <c r="G34" s="76">
+        <v>2</v>
+      </c>
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
@@ -12103,11 +12433,13 @@
       <c r="M34" s="112"/>
       <c r="N34" s="112"/>
       <c r="O34" s="112"/>
-      <c r="P34" s="112"/>
+      <c r="P34" s="112">
+        <v>2</v>
+      </c>
       <c r="Q34" s="120"/>
       <c r="R34" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34" s="124">
         <f t="shared" si="7"/>
@@ -12116,11 +12448,11 @@
       <c r="T34" s="41"/>
       <c r="U34" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V34" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
@@ -12136,30 +12468,42 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>79</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>2</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
       <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
+      <c r="N35" s="112">
+        <v>1</v>
+      </c>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>74</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -12168,15 +12512,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1824</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -12240,11 +12584,15 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>1</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
-      <c r="G37" s="76"/>
+      <c r="G37" s="76">
+        <v>1</v>
+      </c>
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
@@ -12259,11 +12607,13 @@
       <c r="M37" s="112"/>
       <c r="N37" s="112"/>
       <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
+      <c r="P37" s="112">
+        <v>1</v>
+      </c>
       <c r="Q37" s="120"/>
       <c r="R37" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="124">
         <f t="shared" si="7"/>
@@ -12272,11 +12622,11 @@
       <c r="T37" s="41"/>
       <c r="U37" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V37" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
@@ -12292,30 +12642,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4531</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>86</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4445</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>11</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>1</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>74</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -12324,15 +12686,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>26671</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -12448,30 +12810,38 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>95</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>1</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>1</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="7"/>
@@ -12480,15 +12850,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2264</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -12500,30 +12870,38 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>267</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>22</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>2</v>
+      </c>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>20</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -12532,15 +12910,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>2940</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -12595,30 +12973,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>38973</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>980</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>37993</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>304</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>330</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>346</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -12627,15 +13017,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5880</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>227961</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -12691,11 +13081,15 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>1</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
-      <c r="G46" s="76"/>
+      <c r="G46" s="76">
+        <v>1</v>
+      </c>
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
@@ -12710,11 +13104,13 @@
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
       <c r="O46" s="112"/>
-      <c r="P46" s="112"/>
+      <c r="P46" s="112">
+        <v>1</v>
+      </c>
       <c r="Q46" s="120"/>
       <c r="R46" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="128">
         <f t="shared" si="7"/>
@@ -12723,11 +13119,11 @@
       <c r="T46" s="41"/>
       <c r="U46" s="107">
         <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V46" s="134">
         <f t="shared" ref="V46:V47" si="12">U46/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
@@ -12795,30 +13191,38 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2810</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>10</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
+      <c r="P48" s="121">
+        <v>10</v>
+      </c>
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="7"/>
@@ -12827,15 +13231,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16801</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -12847,7 +13251,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -12855,7 +13261,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -12887,7 +13293,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -12899,15 +13305,19 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>2</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
-      <c r="G50" s="76"/>
+      <c r="G50" s="76">
+        <v>1</v>
+      </c>
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -12918,11 +13328,13 @@
       <c r="M50" s="112"/>
       <c r="N50" s="112"/>
       <c r="O50" s="112"/>
-      <c r="P50" s="112"/>
+      <c r="P50" s="112">
+        <v>1</v>
+      </c>
       <c r="Q50" s="120"/>
       <c r="R50" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="124">
         <f t="shared" si="7"/>
@@ -12931,15 +13343,15 @@
       <c r="T50" s="41"/>
       <c r="U50" s="107">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V50" s="130">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -13003,7 +13415,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -13011,7 +13425,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -13043,7 +13457,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -13055,11 +13469,15 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>1</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
-      <c r="G53" s="76"/>
+      <c r="G53" s="76">
+        <v>1</v>
+      </c>
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
@@ -13074,11 +13492,13 @@
       <c r="M53" s="112"/>
       <c r="N53" s="112"/>
       <c r="O53" s="112"/>
-      <c r="P53" s="112"/>
+      <c r="P53" s="112">
+        <v>1</v>
+      </c>
       <c r="Q53" s="120"/>
       <c r="R53" s="96">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="126">
         <f t="shared" si="7"/>
@@ -13087,11 +13507,11 @@
       <c r="T53" s="41"/>
       <c r="U53" s="107">
         <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V53" s="109">
         <f t="shared" ref="V53:V54" si="18">U53/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
@@ -13107,15 +13527,19 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>10</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
-      <c r="G54" s="76"/>
+      <c r="G54" s="76">
+        <v>1</v>
+      </c>
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -13126,11 +13550,13 @@
       <c r="M54" s="112"/>
       <c r="N54" s="112"/>
       <c r="O54" s="112"/>
-      <c r="P54" s="112"/>
+      <c r="P54" s="112">
+        <v>1</v>
+      </c>
       <c r="Q54" s="120"/>
       <c r="R54" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="124">
         <f t="shared" si="7"/>
@@ -13139,15 +13565,15 @@
       <c r="T54" s="41"/>
       <c r="U54" s="107">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V54" s="130">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -13362,11 +13788,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>50709</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -13375,32 +13801,32 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1178</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>49531</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
@@ -13408,7 +13834,7 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
@@ -13416,24 +13842,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1252</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>10416</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1252</v>
+      </c>
+      <c r="W60" s="210">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>371015</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B9BC24-E82C-4FCB-B496-C31D3E160B86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE46A1-7978-4566-A4D5-035A0590702E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -2871,6 +2871,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2939,12 +2945,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3316,15 +3316,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3349,62 +3349,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5655,7 +5655,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5673,7 +5673,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5689,7 +5689,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5705,7 +5705,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5723,7 +5723,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5739,7 +5739,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6134,17 +6134,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46174</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6169,62 +6169,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9718,7 +9718,7 @@
         <f>SUM(V8:V59)</f>
         <v>1302</v>
       </c>
-      <c r="W60" s="209">
+      <c r="W60" s="186">
         <f>SUM(W8:W59)</f>
         <v>379667</v>
       </c>
@@ -9728,7 +9728,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9746,7 +9746,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9762,7 +9762,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9778,7 +9778,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9796,7 +9796,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9812,7 +9812,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10207,17 +10207,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46175</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10242,62 +10242,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13857,7 +13857,7 @@
         <f>SUM(V8:V59)</f>
         <v>1252</v>
       </c>
-      <c r="W60" s="210">
+      <c r="W60" s="187">
         <f>SUM(W8:W59)</f>
         <v>371015</v>
       </c>
@@ -13867,7 +13867,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13885,7 +13885,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13901,7 +13901,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13917,7 +13917,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13935,7 +13935,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13951,7 +13951,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14346,17 +14346,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46176</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14381,62 +14381,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14601,19 +14601,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -14641,7 +14645,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -14676,47 +14680,55 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>98</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>2</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="51"/>
-      <c r="L9" s="121"/>
+      <c r="L9" s="121">
+        <v>2</v>
+      </c>
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
       <c r="P9" s="121"/>
-      <c r="Q9" s="122"/>
+      <c r="Q9" s="122">
+        <v>2</v>
+      </c>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2304</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -14751,47 +14763,55 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>144</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>1</v>
+      </c>
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
-      <c r="Q10" s="120"/>
+      <c r="Q10" s="120">
+        <v>1</v>
+      </c>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3432</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -14826,47 +14846,55 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>33</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>1</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>1</v>
+      </c>
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
-      <c r="Q11" s="120"/>
+      <c r="Q11" s="120">
+        <v>1</v>
+      </c>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -14901,19 +14929,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -14941,7 +14973,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -14976,47 +15008,59 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3145</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>13</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3132</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
         <v>0</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
+      <c r="L13" s="121">
+        <v>13</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
       <c r="N13" s="121"/>
       <c r="O13" s="121"/>
       <c r="P13" s="121"/>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>75168</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -15058,19 +15102,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -15098,7 +15146,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -15133,7 +15181,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -15141,7 +15191,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -15173,7 +15223,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -15358,7 +15408,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -15366,7 +15418,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -15398,7 +15450,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15508,19 +15560,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -15548,7 +15604,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -15583,7 +15639,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -15591,7 +15649,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -15623,7 +15681,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -15658,7 +15716,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -15666,7 +15726,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -15698,7 +15758,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -15734,7 +15794,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -15745,7 +15807,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -15773,7 +15835,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -15815,19 +15877,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -15855,7 +15921,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -15897,7 +15963,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -15905,7 +15973,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -15937,7 +16005,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -15972,22 +16040,30 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>149</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>2</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
+      <c r="L26" s="112">
+        <v>2</v>
+      </c>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
@@ -15995,7 +16071,7 @@
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -16004,15 +16080,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3529</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -16146,15 +16222,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>100</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>2</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -16186,7 +16266,7 @@
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2352</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -16205,19 +16285,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>53</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -16245,7 +16329,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16257,7 +16341,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>13</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -16265,7 +16351,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -16297,7 +16383,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16361,7 +16447,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -16369,7 +16457,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -16401,7 +16489,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -16465,22 +16553,30 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>77</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
@@ -16488,7 +16584,7 @@
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -16497,15 +16593,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1838</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -16621,22 +16717,30 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4445</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>10</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>10</v>
+      </c>
       <c r="M38" s="121"/>
       <c r="N38" s="121"/>
       <c r="O38" s="121"/>
@@ -16644,7 +16748,7 @@
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -16653,15 +16757,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>26611</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -16777,22 +16881,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>94</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>1</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>1</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -16800,7 +16912,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="7"/>
@@ -16809,15 +16921,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2240</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -16829,22 +16941,28 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>245</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>5</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>5</v>
+      </c>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
@@ -16852,7 +16970,7 @@
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -16861,15 +16979,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -16924,22 +17042,30 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>37993</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>441</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>37552</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>441</v>
+      </c>
       <c r="M44" s="121"/>
       <c r="N44" s="121"/>
       <c r="O44" s="121"/>
@@ -16947,7 +17073,7 @@
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -16956,15 +17082,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>2646</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>225315</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -17124,22 +17250,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2800</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>2</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2798</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>2</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -17147,7 +17281,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="7"/>
@@ -17156,15 +17290,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16789</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -17176,7 +17310,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -17184,7 +17320,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -17216,7 +17352,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17228,7 +17364,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>1</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -17236,7 +17374,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -17268,7 +17406,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -17332,7 +17470,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -17340,7 +17480,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -17372,7 +17512,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -17436,7 +17576,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -17444,7 +17586,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -17476,7 +17618,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -17691,11 +17833,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>49530</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -17704,28 +17846,28 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>49049</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
@@ -17741,28 +17883,28 @@
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>3282</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>479</v>
+      </c>
+      <c r="W60" s="187">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>367673</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -17770,7 +17912,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17788,7 +17930,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17804,7 +17946,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17820,7 +17962,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17838,7 +17980,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17854,7 +17996,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18249,17 +18391,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46178</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18284,62 +18426,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21673,7 +21815,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21691,7 +21833,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21707,7 +21849,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21723,7 +21865,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21741,7 +21883,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21757,7 +21899,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22152,17 +22294,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46179</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22187,62 +22329,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25576,7 +25718,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25594,7 +25736,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25610,7 +25752,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25626,7 +25768,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25644,7 +25786,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25660,7 +25802,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26055,17 +26197,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46180</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26090,62 +26232,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -29479,7 +29621,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -29497,7 +29639,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -29513,7 +29655,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -29529,7 +29671,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -29547,7 +29689,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -29563,7 +29705,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -29958,17 +30100,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="191">
+      <c r="P1" s="193">
         <v>46181</v>
       </c>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="193"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="195"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -29993,62 +30135,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="198" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="199" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="200"/>
+      <c r="G4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="206"/>
-      <c r="X4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
+      <c r="R4" s="208"/>
+      <c r="S4" s="208"/>
+      <c r="T4" s="208"/>
+      <c r="U4" s="208"/>
+      <c r="V4" s="209"/>
+      <c r="W4" s="208"/>
+      <c r="X4" s="210"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="204"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -33382,7 +33524,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="186" t="s">
+      <c r="G62" s="188" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -33400,7 +33542,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="187"/>
+      <c r="G63" s="189"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -33416,7 +33558,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="188"/>
+      <c r="G64" s="190"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -33432,7 +33574,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="189" t="s">
+      <c r="G65" s="191" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -33450,7 +33592,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="189"/>
+      <c r="G66" s="191"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -33466,7 +33608,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="190"/>
+      <c r="G67" s="192"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE46A1-7978-4566-A4D5-035A0590702E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF8FDD7-66B4-44E8-A646-D3955DAA3262}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
     <sheet name="05,01" sheetId="117" r:id="rId2"/>
     <sheet name="05,02" sheetId="118" r:id="rId3"/>
     <sheet name="05,03" sheetId="119" r:id="rId4"/>
-    <sheet name="05,05" sheetId="120" r:id="rId5"/>
-    <sheet name="05,06" sheetId="121" r:id="rId6"/>
+    <sheet name="05,04" sheetId="120" r:id="rId5"/>
+    <sheet name="05,05" sheetId="121" r:id="rId6"/>
     <sheet name="05,07" sheetId="122" r:id="rId7"/>
     <sheet name="05,08" sheetId="123" r:id="rId8"/>
   </sheets>
@@ -26,8 +26,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'05,02'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'05,03'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'05,05'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'05,06'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'05,04'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'05,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,07'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
@@ -18646,19 +18646,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -18686,7 +18690,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -18721,7 +18725,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -18729,7 +18735,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -18761,7 +18767,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2304</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -18796,15 +18802,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>143</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>4</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -18813,13 +18823,17 @@
       <c r="K10" s="41"/>
       <c r="L10" s="112"/>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>2</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -18828,15 +18842,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3336</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -18871,15 +18885,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>32</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>9</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -18888,13 +18906,17 @@
       <c r="K11" s="41"/>
       <c r="L11" s="112"/>
       <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="N11" s="112">
+        <v>2</v>
+      </c>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>7</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -18903,15 +18925,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -18946,19 +18968,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -18986,7 +19012,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -19021,47 +19047,61 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3132</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>41</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3091</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="L13" s="121">
+        <v>10</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>7</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="P13" s="121">
+        <v>24</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>74172</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -19103,19 +19143,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -19143,7 +19187,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -19178,7 +19222,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -19186,7 +19232,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -19218,7 +19264,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -19403,7 +19449,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -19411,7 +19459,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -19443,7 +19491,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -19553,19 +19601,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -19593,7 +19645,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -19628,7 +19680,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -19636,7 +19690,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -19668,7 +19722,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -19703,7 +19757,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -19711,7 +19767,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -19743,7 +19799,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -19779,7 +19835,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -19790,7 +19848,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -19818,7 +19876,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -19860,19 +19918,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -19900,7 +19962,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -19942,7 +20004,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -19950,7 +20014,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -19982,7 +20046,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -20017,30 +20081,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>147</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>20</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>20</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -20049,15 +20121,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3049</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -20191,30 +20263,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>98</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>46</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>26</v>
+      </c>
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>20</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -20223,15 +20303,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1248</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -20250,19 +20330,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>53</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -20290,7 +20374,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -20302,7 +20386,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>13</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -20310,7 +20396,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -20342,7 +20428,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -20406,7 +20492,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -20414,7 +20502,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -20446,7 +20534,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -20510,19 +20598,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>76</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -20550,7 +20642,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1838</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -20666,30 +20758,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4435</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>275</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4160</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>117</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>23</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>135</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -20698,15 +20802,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>24961</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -20822,22 +20926,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>93</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>65</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>65</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -20845,7 +20957,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="7"/>
@@ -20854,15 +20966,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -20874,30 +20986,40 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>240</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>71</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>50</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>1</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>20</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -20906,15 +21028,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>2028</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -20969,30 +21091,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>37552</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1206</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>36346</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>370</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>297</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>539</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -21001,15 +21135,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7236</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>218079</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -21169,22 +21303,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2798</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>3</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2795</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>3</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -21192,7 +21334,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="7"/>
@@ -21201,15 +21343,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16771</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -21221,7 +21363,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -21229,7 +21373,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -21261,7 +21405,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -21273,11 +21417,15 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>1</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
-      <c r="G50" s="76"/>
+      <c r="G50" s="76">
+        <v>1</v>
+      </c>
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
@@ -21292,11 +21440,13 @@
       <c r="M50" s="112"/>
       <c r="N50" s="112"/>
       <c r="O50" s="112"/>
-      <c r="P50" s="112"/>
+      <c r="P50" s="112">
+        <v>1</v>
+      </c>
       <c r="Q50" s="120"/>
       <c r="R50" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="124">
         <f t="shared" si="7"/>
@@ -21305,11 +21455,11 @@
       <c r="T50" s="41"/>
       <c r="U50" s="107">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V50" s="130">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
@@ -21377,7 +21527,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -21385,7 +21537,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -21417,7 +21569,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -21481,7 +21633,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -21489,7 +21643,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -21521,7 +21675,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -21736,11 +21890,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>49049</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -21749,32 +21903,32 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>47308</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
@@ -21782,7 +21936,7 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
@@ -21790,24 +21944,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>14220</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1741</v>
+      </c>
+      <c r="W60" s="187">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>353441</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -22549,19 +22703,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -22589,7 +22747,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -22624,7 +22782,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -22632,7 +22792,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -22664,7 +22824,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2304</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -22699,7 +22859,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>139</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -22707,7 +22869,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -22739,7 +22901,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3336</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -22774,7 +22936,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>23</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -22782,7 +22946,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -22814,7 +22978,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -22849,19 +23013,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -22889,7 +23057,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -22924,15 +23092,23 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3090</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>17</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3073</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
@@ -22941,30 +23117,36 @@
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="N13" s="121">
+        <v>9</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="P13" s="121">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>73752</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -23006,19 +23188,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -23046,7 +23232,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -23081,7 +23267,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -23089,7 +23277,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -23121,7 +23309,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -23306,7 +23494,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -23314,7 +23504,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -23346,7 +23536,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -23456,19 +23646,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -23496,7 +23690,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -23531,7 +23725,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -23539,7 +23735,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -23571,7 +23767,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -23606,7 +23802,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -23614,7 +23812,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -23646,7 +23844,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -23682,7 +23880,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -23693,7 +23893,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -23721,7 +23921,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -23763,19 +23963,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -23803,7 +24007,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -23845,7 +24049,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -23853,7 +24059,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -23885,7 +24091,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -23920,30 +24126,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>127</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>2</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -23952,15 +24166,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3001</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -24094,15 +24308,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>52</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>4</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -24113,11 +24331,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -24126,15 +24346,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -24153,19 +24373,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>53</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -24193,7 +24417,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -24205,15 +24429,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>13</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -24224,11 +24452,13 @@
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="7"/>
@@ -24237,15 +24467,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -24309,7 +24539,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -24317,7 +24549,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -24349,7 +24581,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -24413,30 +24645,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>76</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>2</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>2</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -24445,15 +24685,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1790</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -24569,30 +24809,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4160</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>52</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4108</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>6</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>46</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -24601,15 +24851,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>24649</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -24725,19 +24975,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>28</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -24765,7 +25019,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -24777,15 +25031,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>169</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>24</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
@@ -24794,13 +25052,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>4</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>20</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -24809,15 +25071,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -24872,30 +25134,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>36346</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>773</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>35573</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>384</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>389</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -24904,15 +25176,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>4638</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>213441</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -25072,19 +25344,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2795</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2795</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -25112,7 +25388,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16771</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -25124,15 +25400,16 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
       <c r="G49" s="76"/>
       <c r="H49" s="73"/>
       <c r="I49" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -25164,7 +25441,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -25280,7 +25557,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -25288,7 +25567,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -25320,7 +25599,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -25384,7 +25663,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -25392,7 +25673,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -25424,7 +25705,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -25639,11 +25920,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>47307</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -25652,19 +25933,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>46432</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -25677,7 +25958,7 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
@@ -25685,32 +25966,32 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>5862</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>875</v>
+      </c>
+      <c r="W60" s="187">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>347567</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF8FDD7-66B4-44E8-A646-D3955DAA3262}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B546202A-BD4F-49AF-9CB9-EFD2FC5FDBA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="05,03" sheetId="119" r:id="rId4"/>
     <sheet name="05,04" sheetId="120" r:id="rId5"/>
     <sheet name="05,05" sheetId="121" r:id="rId6"/>
-    <sheet name="05,07" sheetId="122" r:id="rId7"/>
-    <sheet name="05,08" sheetId="123" r:id="rId8"/>
+    <sheet name="05,08" sheetId="123" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -28,8 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'05,03'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05,04'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,05'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'05,07'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'05,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -569,92 +567,6 @@
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{98075FA3-BE24-4F4B-81CE-01CE36E1C6E4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory 
-Bottle Per Case
-All Route</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{FE74051E-2C0D-4632-AE6D-BCB6DE08186C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory
-Per Case</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{C43CE2EF-2F8B-4C4E-8996-CA31CB0252DD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Ending Inventory
-Bottle Per Case</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
     <comment ref="U5" authorId="0" shapeId="0" xr:uid="{078BB2F2-7AE2-4DF4-9255-866BCB109AED}">
       <text>
         <r>
@@ -736,7 +648,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -26429,7 +26341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2A4E04-B047-4EF0-8B6B-8B0A50F08BA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35485E88-8B9C-421D-9E16-DE6F175C77AB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26479,7 +26391,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="193">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="Q1" s="194"/>
       <c r="R1" s="194"/>
@@ -26733,19 +26645,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -26773,7 +26689,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -26808,7 +26724,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -26816,7 +26734,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -26848,7 +26766,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2304</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -26883,7 +26801,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>139</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -26891,7 +26811,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -26923,7 +26843,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3336</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -26958,7 +26878,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>23</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -26966,7 +26888,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -26998,7 +26920,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -27033,19 +26955,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -27073,7 +26999,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -27108,47 +27034,59 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3073</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>25</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3048</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="N13" s="121">
+        <v>15</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="P13" s="121">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>73140</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -27190,19 +27128,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -27230,7 +27172,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -27265,7 +27207,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -27273,7 +27217,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -27305,7 +27249,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -27490,7 +27434,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -27498,7 +27444,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -27530,7 +27476,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -27640,19 +27586,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -27680,7 +27630,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -27715,7 +27665,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -27723,7 +27675,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
@@ -27755,7 +27707,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -27790,7 +27742,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -27798,7 +27752,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -27830,7 +27784,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -27866,7 +27820,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -27877,7 +27833,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -27905,7 +27861,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -27947,19 +27903,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -27987,7 +27947,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -28029,7 +27989,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -28037,7 +27999,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -28069,7 +28031,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -28104,30 +28066,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>125</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>1</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -28136,15 +28106,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2977</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -28278,15 +28248,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>48</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>5</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -28297,11 +28271,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>5</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -28310,15 +28286,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -28337,19 +28313,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>53</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -28377,7 +28357,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -28389,7 +28369,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -28397,7 +28379,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -28429,7 +28411,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -28493,7 +28475,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -28501,7 +28485,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -28533,7 +28517,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -28597,19 +28581,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>74</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -28637,7 +28625,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1790</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -28753,30 +28741,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4108</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>109</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3999</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>33</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>76</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -28785,15 +28783,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>23995</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -28909,19 +28907,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>28</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -28949,7 +28951,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -28961,15 +28963,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>145</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>14</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
@@ -28978,13 +28984,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>4</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>10</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -28993,15 +29003,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>1572</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -29056,30 +29066,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>35573</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>873</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>34700</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>457</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>416</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>873</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -29088,15 +29108,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5238</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>873</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>208203</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -29256,19 +29276,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2795</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2795</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -29296,7 +29320,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16771</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -29308,7 +29332,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -29316,7 +29342,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -29348,7 +29374,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -29464,7 +29490,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -29472,7 +29500,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -29504,7 +29532,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -29568,7 +29596,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -29576,7 +29606,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -29608,7 +29638,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -29823,11 +29853,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>46432</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -29836,19 +29866,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>45405</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -29861,7 +29891,7 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
@@ -29869,3935 +29899,32 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>6804</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1027</v>
+      </c>
+      <c r="W60" s="187">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
-      </c>
-      <c r="X60" s="45"/>
-    </row>
-    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="V61" s="103"/>
-    </row>
-    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
-        <v>65</v>
-      </c>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="L62" s="30"/>
-      <c r="M62" s="62"/>
-      <c r="N62" s="31"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="67"/>
-      <c r="R62" s="67"/>
-      <c r="S62" s="32"/>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
-      <c r="J63" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="L63" s="33"/>
-      <c r="M63" s="63"/>
-      <c r="N63" s="34"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="68"/>
-      <c r="R63" s="68"/>
-      <c r="S63" s="35"/>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="L64" s="36"/>
-      <c r="M64" s="64"/>
-      <c r="N64" s="37"/>
-      <c r="O64" s="37"/>
-      <c r="P64" s="37"/>
-      <c r="Q64" s="69"/>
-      <c r="R64" s="69"/>
-      <c r="S64" s="38"/>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
-        <v>64</v>
-      </c>
-      <c r="H65" s="60"/>
-      <c r="I65" s="60"/>
-      <c r="J65" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="L65" s="36"/>
-      <c r="M65" s="64"/>
-      <c r="N65" s="37"/>
-      <c r="O65" s="37"/>
-      <c r="P65" s="37"/>
-      <c r="Q65" s="69"/>
-      <c r="R65" s="69"/>
-      <c r="S65" s="38"/>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
-      <c r="H66" s="60"/>
-      <c r="I66" s="60"/>
-      <c r="J66" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="L66" s="33"/>
-      <c r="M66" s="63"/>
-      <c r="N66" s="34"/>
-      <c r="O66" s="34"/>
-      <c r="P66" s="34"/>
-      <c r="Q66" s="68"/>
-      <c r="R66" s="68"/>
-      <c r="S66" s="35"/>
-    </row>
-    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
-      <c r="J67" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="L67" s="39"/>
-      <c r="M67" s="65"/>
-      <c r="N67" s="40"/>
-      <c r="O67" s="40"/>
-      <c r="P67" s="40"/>
-      <c r="Q67" s="70"/>
-      <c r="R67" s="70"/>
-      <c r="S67" s="29"/>
-    </row>
-    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C69" s="183" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="184"/>
-      <c r="E69" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="M69" s="66"/>
-      <c r="N69" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="O69" s="20"/>
-      <c r="P69" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q69" s="71"/>
-      <c r="R69" s="71"/>
-      <c r="S69" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="X69" s="101" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B70" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="22"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="11"/>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="11"/>
-      <c r="S70" s="11"/>
-      <c r="X70" s="22"/>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B71" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
-      <c r="R71" s="22"/>
-      <c r="S71" s="22"/>
-      <c r="X71" s="22"/>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B72" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="X72" s="22"/>
-    </row>
-    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B74" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="X74" s="22"/>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B75" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="X75" s="22"/>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B76" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="L76" s="22"/>
-      <c r="M76" s="22"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="22"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="22"/>
-      <c r="R76" s="22"/>
-      <c r="S76" s="22"/>
-      <c r="X76" s="22"/>
-    </row>
-    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B78" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="L78" s="22"/>
-      <c r="M78" s="22"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="22"/>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="X78" s="22"/>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B79" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="L79" s="22"/>
-      <c r="M79" s="22"/>
-      <c r="N79" s="22"/>
-      <c r="O79" s="22"/>
-      <c r="P79" s="22"/>
-      <c r="Q79" s="22"/>
-      <c r="R79" s="22"/>
-      <c r="S79" s="22"/>
-      <c r="X79" s="22"/>
-    </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B80" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
-      <c r="R80" s="22"/>
-      <c r="S80" s="22"/>
-      <c r="X80" s="22"/>
-    </row>
-    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B82" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="L82" s="22"/>
-      <c r="M82" s="22"/>
-      <c r="N82" s="22"/>
-      <c r="O82" s="22"/>
-      <c r="P82" s="22"/>
-      <c r="Q82" s="22"/>
-      <c r="R82" s="22"/>
-      <c r="S82" s="22"/>
-      <c r="X82" s="22"/>
-    </row>
-    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B83" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="L83" s="22"/>
-      <c r="M83" s="22"/>
-      <c r="N83" s="22"/>
-      <c r="O83" s="22"/>
-      <c r="P83" s="22"/>
-      <c r="Q83" s="22"/>
-      <c r="R83" s="22"/>
-      <c r="S83" s="22"/>
-      <c r="X83" s="22"/>
-    </row>
-    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B84" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="22"/>
-      <c r="L84" s="22"/>
-      <c r="M84" s="22"/>
-      <c r="N84" s="22"/>
-      <c r="O84" s="22"/>
-      <c r="P84" s="22"/>
-      <c r="Q84" s="22"/>
-      <c r="R84" s="22"/>
-      <c r="S84" s="22"/>
-      <c r="X84" s="22"/>
-    </row>
-    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B86" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
-      <c r="L86" s="22"/>
-      <c r="M86" s="22"/>
-      <c r="N86" s="22"/>
-      <c r="O86" s="22"/>
-      <c r="P86" s="22"/>
-      <c r="Q86" s="22"/>
-      <c r="R86" s="22"/>
-      <c r="S86" s="22"/>
-      <c r="X86" s="22"/>
-    </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B87" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22"/>
-      <c r="E87" s="22"/>
-      <c r="L87" s="22"/>
-      <c r="M87" s="22"/>
-      <c r="N87" s="22"/>
-      <c r="O87" s="22"/>
-      <c r="P87" s="22"/>
-      <c r="Q87" s="22"/>
-      <c r="R87" s="22"/>
-      <c r="S87" s="22"/>
-      <c r="X87" s="22"/>
-    </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B88" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="L88" s="22"/>
-      <c r="M88" s="22"/>
-      <c r="N88" s="22"/>
-      <c r="O88" s="22"/>
-      <c r="P88" s="22"/>
-      <c r="Q88" s="22"/>
-      <c r="R88" s="22"/>
-      <c r="S88" s="22"/>
-      <c r="X88" s="22"/>
-    </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B90" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22"/>
-      <c r="L90" s="22"/>
-      <c r="M90" s="22"/>
-      <c r="N90" s="22"/>
-      <c r="O90" s="22"/>
-      <c r="P90" s="22"/>
-      <c r="Q90" s="22"/>
-      <c r="R90" s="22"/>
-      <c r="S90" s="22"/>
-      <c r="X90" s="22"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="P1:X1"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:X4"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35485E88-8B9C-421D-9E16-DE6F175C77AB}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BH90"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2" style="2" customWidth="1"/>
-    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
-    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
-    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
-    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
-    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="61" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="193">
-        <v>46181</v>
-      </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
-    </row>
-    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-    </row>
-    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="197" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="198" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="199" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="203" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="205" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="203" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" s="207" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
-    </row>
-    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="185" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
-      <c r="L5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M5" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" s="87" t="s">
-        <v>13</v>
-      </c>
-      <c r="S5" s="83" t="s">
-        <v>75</v>
-      </c>
-      <c r="T5" s="7"/>
-      <c r="U5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="V5" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="W5" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="X5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
-      <c r="AV5" s="9"/>
-      <c r="AW5" s="9"/>
-      <c r="AX5" s="9"/>
-      <c r="AY5" s="9"/>
-      <c r="AZ5" s="9"/>
-      <c r="BA5" s="9"/>
-      <c r="BB5" s="9"/>
-      <c r="BC5" s="9"/>
-      <c r="BD5" s="9"/>
-      <c r="BE5" s="9"/>
-      <c r="BF5" s="9"/>
-      <c r="BG5" s="9"/>
-      <c r="BH5" s="9"/>
-    </row>
-    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="10"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="123"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="107"/>
-      <c r="V6" s="109"/>
-      <c r="W6" s="129"/>
-      <c r="X6" s="27"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="9"/>
-      <c r="AQ6" s="9"/>
-      <c r="AR6" s="9"/>
-      <c r="AS6" s="9"/>
-      <c r="AT6" s="9"/>
-      <c r="AU6" s="9"/>
-      <c r="AV6" s="9"/>
-      <c r="AW6" s="9"/>
-      <c r="AX6" s="9"/>
-      <c r="AY6" s="9"/>
-      <c r="AZ6" s="9"/>
-      <c r="BA6" s="9"/>
-      <c r="BB6" s="9"/>
-      <c r="BC6" s="9"/>
-      <c r="BD6" s="9"/>
-      <c r="BE6" s="9"/>
-      <c r="BF6" s="9"/>
-      <c r="BG6" s="9"/>
-      <c r="BH6" s="9"/>
-    </row>
-    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="10"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="119"/>
-      <c r="R7" s="88"/>
-      <c r="S7" s="123"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="107"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="27"/>
-      <c r="AL7" s="9"/>
-      <c r="AM7" s="9"/>
-      <c r="AN7" s="9"/>
-      <c r="AO7" s="9"/>
-      <c r="AP7" s="9"/>
-      <c r="AQ7" s="9"/>
-      <c r="AR7" s="9"/>
-      <c r="AS7" s="9"/>
-      <c r="AT7" s="9"/>
-      <c r="AU7" s="9"/>
-      <c r="AV7" s="9"/>
-      <c r="AW7" s="9"/>
-      <c r="AX7" s="9"/>
-      <c r="AY7" s="9"/>
-      <c r="AZ7" s="9"/>
-      <c r="BA7" s="9"/>
-      <c r="BB7" s="9"/>
-      <c r="BC7" s="9"/>
-      <c r="BD7" s="9"/>
-      <c r="BE7" s="9"/>
-      <c r="BF7" s="9"/>
-      <c r="BG7" s="9"/>
-      <c r="BH7" s="9"/>
-    </row>
-    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>1</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73">
-        <f>C8-G8</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="77">
-        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="120"/>
-      <c r="R8" s="86">
-        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="41"/>
-      <c r="U8" s="107">
-        <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="130">
-        <f>U8/24</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="129">
-        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
-      </c>
-      <c r="X8" s="27"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-      <c r="BC8" s="12"/>
-      <c r="BD8" s="12"/>
-      <c r="BE8" s="12"/>
-      <c r="BF8" s="12"/>
-      <c r="BG8" s="12"/>
-      <c r="BH8" s="12"/>
-    </row>
-    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <f t="shared" ref="A9:A59" si="3">A8+1</f>
-        <v>2</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="78">
-        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="94">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="51"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="98">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="125">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="51"/>
-      <c r="U9" s="131">
-        <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="132">
-        <f>U9/24</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="133">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="52"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="12"/>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="12"/>
-      <c r="AS9" s="12"/>
-      <c r="AT9" s="12"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="12"/>
-      <c r="AX9" s="12"/>
-      <c r="AY9" s="12"/>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="12"/>
-      <c r="BC9" s="12"/>
-      <c r="BD9" s="12"/>
-      <c r="BE9" s="12"/>
-      <c r="BF9" s="12"/>
-      <c r="BG9" s="12"/>
-      <c r="BH9" s="12"/>
-    </row>
-    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="95">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="41"/>
-      <c r="U10" s="107">
-        <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="134">
-        <f>U10/24</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="129">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="27"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12"/>
-      <c r="AY10" s="12"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="12"/>
-      <c r="BD10" s="12"/>
-      <c r="BE10" s="12"/>
-      <c r="BF10" s="12"/>
-      <c r="BG10" s="12"/>
-      <c r="BH10" s="12"/>
-    </row>
-    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
-      <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
-      <c r="Q11" s="120"/>
-      <c r="R11" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="41"/>
-      <c r="U11" s="107">
-        <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="130">
-        <f>U11/24</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="129">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="27"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="12"/>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
-      <c r="AS11" s="12"/>
-      <c r="AT11" s="12"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="12"/>
-      <c r="AX11" s="12"/>
-      <c r="AY11" s="12"/>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="12"/>
-      <c r="BC11" s="12"/>
-      <c r="BD11" s="12"/>
-      <c r="BE11" s="12"/>
-      <c r="BF11" s="12"/>
-      <c r="BG11" s="12"/>
-      <c r="BH11" s="12"/>
-    </row>
-    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="77">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="41"/>
-      <c r="L12" s="112"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="41"/>
-      <c r="U12" s="107">
-        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="130">
-        <f t="shared" ref="V12:V41" si="6">U12/24</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="129">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="27"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-      <c r="BC12" s="12"/>
-      <c r="BD12" s="12"/>
-      <c r="BE12" s="12"/>
-      <c r="BF12" s="12"/>
-      <c r="BG12" s="12"/>
-      <c r="BH12" s="12"/>
-    </row>
-    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="80">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="94">
-        <f>D13-H13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
-      <c r="R13" s="97">
-        <f>L13+N13+P13</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="125">
-        <f>M13+O13+Q13</f>
-        <v>0</v>
-      </c>
-      <c r="T13" s="53"/>
-      <c r="U13" s="131">
-        <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="135">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="133">
-        <f>I13*24+J13</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="12"/>
-      <c r="AM13" s="12"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="12"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="12"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="12"/>
-      <c r="AX13" s="12"/>
-      <c r="AY13" s="12"/>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="12"/>
-      <c r="BC13" s="12"/>
-      <c r="BD13" s="12"/>
-      <c r="BE13" s="12"/>
-      <c r="BF13" s="12"/>
-      <c r="BG13" s="12"/>
-      <c r="BH13" s="12"/>
-    </row>
-    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="93">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="95">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="96">
-        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="126">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="41"/>
-      <c r="U14" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="109">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="129">
-        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
-      </c>
-      <c r="X14" s="27"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="12"/>
-      <c r="AX14" s="12"/>
-      <c r="AY14" s="12"/>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12"/>
-      <c r="BC14" s="12"/>
-      <c r="BD14" s="12"/>
-      <c r="BE14" s="12"/>
-      <c r="BF14" s="12"/>
-      <c r="BG14" s="12"/>
-      <c r="BH14" s="12"/>
-    </row>
-    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="120"/>
-      <c r="R15" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="41"/>
-      <c r="U15" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="27"/>
-      <c r="AL15" s="12"/>
-      <c r="AM15" s="12"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="12"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="12"/>
-      <c r="AT15" s="12"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="12"/>
-      <c r="AX15" s="12"/>
-      <c r="AY15" s="12"/>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="12"/>
-      <c r="BC15" s="12"/>
-      <c r="BD15" s="12"/>
-      <c r="BE15" s="12"/>
-      <c r="BF15" s="12"/>
-      <c r="BG15" s="12"/>
-      <c r="BH15" s="12"/>
-    </row>
-    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="41"/>
-      <c r="U16" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="27"/>
-      <c r="AL16" s="12"/>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
-      <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-      <c r="BC16" s="12"/>
-      <c r="BD16" s="12"/>
-      <c r="BE16" s="12"/>
-      <c r="BF16" s="12"/>
-      <c r="BG16" s="12"/>
-      <c r="BH16" s="12"/>
-    </row>
-    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="112"/>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="120"/>
-      <c r="R17" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="41"/>
-      <c r="U17" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="27"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-      <c r="AS17" s="12"/>
-      <c r="AT17" s="12"/>
-      <c r="AU17" s="12"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="12"/>
-      <c r="AX17" s="12"/>
-      <c r="AY17" s="12"/>
-      <c r="AZ17" s="12"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="12"/>
-      <c r="BC17" s="12"/>
-      <c r="BD17" s="12"/>
-      <c r="BE17" s="12"/>
-      <c r="BF17" s="12"/>
-      <c r="BG17" s="12"/>
-      <c r="BH17" s="12"/>
-    </row>
-    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="41"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="120"/>
-      <c r="R18" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="41"/>
-      <c r="U18" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="27"/>
-      <c r="AL18" s="12"/>
-      <c r="AM18" s="12"/>
-      <c r="AN18" s="12"/>
-      <c r="AO18" s="12"/>
-      <c r="AP18" s="12"/>
-      <c r="AQ18" s="12"/>
-      <c r="AR18" s="12"/>
-      <c r="AS18" s="12"/>
-      <c r="AT18" s="12"/>
-      <c r="AU18" s="12"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="12"/>
-      <c r="AX18" s="12"/>
-      <c r="AY18" s="12"/>
-      <c r="AZ18" s="12"/>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="12"/>
-      <c r="BC18" s="12"/>
-      <c r="BD18" s="12"/>
-      <c r="BE18" s="12"/>
-      <c r="BF18" s="12"/>
-      <c r="BG18" s="12"/>
-      <c r="BH18" s="12"/>
-    </row>
-    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="41"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="120"/>
-      <c r="R19" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="41"/>
-      <c r="U19" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="27"/>
-      <c r="AL19" s="12"/>
-      <c r="AM19" s="12"/>
-      <c r="AN19" s="12"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="12"/>
-      <c r="AQ19" s="12"/>
-      <c r="AR19" s="12"/>
-      <c r="AS19" s="12"/>
-      <c r="AT19" s="12"/>
-      <c r="AU19" s="12"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="12"/>
-      <c r="AX19" s="12"/>
-      <c r="AY19" s="12"/>
-      <c r="AZ19" s="12"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="12"/>
-      <c r="BC19" s="12"/>
-      <c r="BD19" s="12"/>
-      <c r="BE19" s="12"/>
-      <c r="BF19" s="12"/>
-      <c r="BG19" s="12"/>
-      <c r="BH19" s="12"/>
-    </row>
-    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="41"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="112"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="112"/>
-      <c r="Q20" s="120"/>
-      <c r="R20" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="41"/>
-      <c r="U20" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="27"/>
-      <c r="AL20" s="12"/>
-      <c r="AM20" s="12"/>
-      <c r="AN20" s="12"/>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="12"/>
-      <c r="AQ20" s="12"/>
-      <c r="AR20" s="12"/>
-      <c r="AS20" s="12"/>
-      <c r="AT20" s="12"/>
-      <c r="AU20" s="12"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="12"/>
-      <c r="AX20" s="12"/>
-      <c r="AY20" s="12"/>
-      <c r="AZ20" s="12"/>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="12"/>
-      <c r="BC20" s="12"/>
-      <c r="BD20" s="12"/>
-      <c r="BE20" s="12"/>
-      <c r="BF20" s="12"/>
-      <c r="BG20" s="12"/>
-      <c r="BH20" s="12"/>
-    </row>
-    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="112"/>
-      <c r="F21" s="112"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="41"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="112"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="120"/>
-      <c r="R21" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="41"/>
-      <c r="U21" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="27"/>
-      <c r="AL21" s="12"/>
-      <c r="AM21" s="12"/>
-      <c r="AN21" s="12"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="12"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
-      <c r="AS21" s="12"/>
-      <c r="AT21" s="12"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="12"/>
-      <c r="AX21" s="12"/>
-      <c r="AY21" s="12"/>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-      <c r="BC21" s="12"/>
-      <c r="BD21" s="12"/>
-      <c r="BE21" s="12"/>
-      <c r="BF21" s="12"/>
-      <c r="BG21" s="12"/>
-      <c r="BH21" s="12"/>
-    </row>
-    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="112"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="41"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="112"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="120"/>
-      <c r="R22" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="41"/>
-      <c r="U22" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="27"/>
-      <c r="AL22" s="12"/>
-      <c r="AM22" s="12"/>
-      <c r="AN22" s="12"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="12"/>
-      <c r="AQ22" s="12"/>
-      <c r="AR22" s="12"/>
-      <c r="AS22" s="12"/>
-      <c r="AT22" s="12"/>
-      <c r="AU22" s="12"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="12"/>
-      <c r="AX22" s="12"/>
-      <c r="AY22" s="12"/>
-      <c r="AZ22" s="12"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="12"/>
-      <c r="BC22" s="12"/>
-      <c r="BD22" s="12"/>
-      <c r="BE22" s="12"/>
-      <c r="BF22" s="12"/>
-      <c r="BG22" s="12"/>
-      <c r="BH22" s="12"/>
-    </row>
-    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="112"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="42"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="120"/>
-      <c r="R23" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="42"/>
-      <c r="U23" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="12"/>
-      <c r="AM23" s="12"/>
-      <c r="AN23" s="12"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="12"/>
-      <c r="AQ23" s="12"/>
-      <c r="AR23" s="12"/>
-      <c r="AS23" s="12"/>
-      <c r="AT23" s="12"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="12"/>
-      <c r="AX23" s="12"/>
-      <c r="AY23" s="12"/>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-      <c r="BC23" s="12"/>
-      <c r="BD23" s="12"/>
-      <c r="BE23" s="12"/>
-      <c r="BF23" s="12"/>
-      <c r="BG23" s="12"/>
-      <c r="BH23" s="12"/>
-    </row>
-    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="42"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="112"/>
-      <c r="N24" s="112"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="112"/>
-      <c r="Q24" s="120"/>
-      <c r="R24" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="42"/>
-      <c r="U24" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="27"/>
-      <c r="Y24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="12"/>
-      <c r="AM24" s="12"/>
-      <c r="AN24" s="12"/>
-      <c r="AO24" s="12"/>
-      <c r="AP24" s="12"/>
-      <c r="AQ24" s="12"/>
-      <c r="AR24" s="12"/>
-      <c r="AS24" s="12"/>
-      <c r="AT24" s="12"/>
-      <c r="AU24" s="12"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="12"/>
-      <c r="AX24" s="12"/>
-      <c r="AY24" s="12"/>
-      <c r="AZ24" s="12"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="12"/>
-      <c r="BC24" s="12"/>
-      <c r="BD24" s="12"/>
-      <c r="BE24" s="12"/>
-      <c r="BF24" s="12"/>
-      <c r="BG24" s="12"/>
-      <c r="BH24" s="12"/>
-    </row>
-    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="41"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="112"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
-      <c r="Q25" s="120"/>
-      <c r="R25" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="41"/>
-      <c r="U25" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="27"/>
-      <c r="AL25" s="12"/>
-      <c r="AM25" s="12"/>
-      <c r="AN25" s="12"/>
-      <c r="AO25" s="12"/>
-      <c r="AP25" s="12"/>
-      <c r="AQ25" s="12"/>
-      <c r="AR25" s="12"/>
-      <c r="AS25" s="12"/>
-      <c r="AT25" s="12"/>
-      <c r="AU25" s="12"/>
-      <c r="AV25" s="12"/>
-      <c r="AW25" s="12"/>
-      <c r="AX25" s="12"/>
-      <c r="AY25" s="12"/>
-      <c r="AZ25" s="12"/>
-      <c r="BA25" s="12"/>
-      <c r="BB25" s="12"/>
-      <c r="BC25" s="12"/>
-      <c r="BD25" s="12"/>
-      <c r="BE25" s="12"/>
-      <c r="BF25" s="12"/>
-      <c r="BG25" s="12"/>
-      <c r="BH25" s="12"/>
-    </row>
-    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="120"/>
-      <c r="R26" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="41"/>
-      <c r="U26" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="27"/>
-      <c r="BE26" s="14" t="e">
-        <f>#REF!-BE25</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="42"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="120"/>
-      <c r="R27" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="42"/>
-      <c r="U27" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="2"/>
-      <c r="AD27" s="2"/>
-      <c r="AG27" s="2"/>
-      <c r="AH27" s="2"/>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
-      <c r="AK27" s="2"/>
-    </row>
-    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="42"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="120"/>
-      <c r="R28" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="42"/>
-      <c r="U28" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="2"/>
-      <c r="AD28" s="2"/>
-      <c r="AG28" s="2"/>
-      <c r="AH28" s="2"/>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-    </row>
-    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="42"/>
-      <c r="U29" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="2"/>
-      <c r="AD29" s="2"/>
-      <c r="AG29" s="2"/>
-      <c r="AH29" s="2"/>
-      <c r="AI29" s="2"/>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
-    </row>
-    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="120"/>
-      <c r="R30" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="41"/>
-      <c r="U30" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="27"/>
-    </row>
-    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="110"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="41"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="120"/>
-      <c r="R31" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="41"/>
-      <c r="U31" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="27"/>
-    </row>
-    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="110"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="112"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="41"/>
-      <c r="L32" s="112"/>
-      <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="120"/>
-      <c r="R32" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="41"/>
-      <c r="U32" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="27"/>
-    </row>
-    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="110"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="112"/>
-      <c r="F33" s="112"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="41"/>
-      <c r="L33" s="112"/>
-      <c r="M33" s="112"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="112"/>
-      <c r="P33" s="112"/>
-      <c r="Q33" s="120"/>
-      <c r="R33" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="41"/>
-      <c r="U33" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="27"/>
-    </row>
-    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="110"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="112"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="41"/>
-      <c r="L34" s="112"/>
-      <c r="M34" s="112"/>
-      <c r="N34" s="112"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="112"/>
-      <c r="Q34" s="120"/>
-      <c r="R34" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T34" s="41"/>
-      <c r="U34" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="27"/>
-    </row>
-    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="112"/>
-      <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
-      <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
-      <c r="Q35" s="120"/>
-      <c r="R35" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T35" s="41"/>
-      <c r="U35" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X35" s="27"/>
-    </row>
-    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="110"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="41"/>
-      <c r="L36" s="112"/>
-      <c r="M36" s="112"/>
-      <c r="N36" s="112"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="112"/>
-      <c r="Q36" s="120"/>
-      <c r="R36" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T36" s="41"/>
-      <c r="U36" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V36" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="27"/>
-    </row>
-    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="110"/>
-      <c r="D37" s="111"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="41"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112"/>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="120"/>
-      <c r="R37" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T37" s="41"/>
-      <c r="U37" s="107">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V37" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="129">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="27"/>
-    </row>
-    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
-        <f t="shared" si="3"/>
-        <v>31</v>
-      </c>
-      <c r="B38" s="138" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="139">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="140">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
-      <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
-      <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
-      <c r="Q38" s="122"/>
-      <c r="R38" s="97">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="125">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T38" s="51"/>
-      <c r="U38" s="131">
-        <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="135">
-        <f>U38/6</f>
-        <v>0</v>
-      </c>
-      <c r="W38" s="133">
-        <f>I38*6+J38</f>
-        <v>0</v>
-      </c>
-      <c r="X38" s="52"/>
-    </row>
-    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="110"/>
-      <c r="D39" s="111"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="76">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="41"/>
-      <c r="L39" s="112"/>
-      <c r="M39" s="112"/>
-      <c r="N39" s="112"/>
-      <c r="O39" s="112"/>
-      <c r="P39" s="112"/>
-      <c r="Q39" s="120"/>
-      <c r="R39" s="96">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="126">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T39" s="41"/>
-      <c r="U39" s="107">
-        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="109">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W39" s="129">
-        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
-      </c>
-      <c r="X39" s="27"/>
-    </row>
-    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-      <c r="B40" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="116"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="41"/>
-      <c r="L40" s="112"/>
-      <c r="M40" s="112"/>
-      <c r="N40" s="112"/>
-      <c r="O40" s="112"/>
-      <c r="P40" s="112"/>
-      <c r="Q40" s="120"/>
-      <c r="R40" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T40" s="41"/>
-      <c r="U40" s="136">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V40" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="137">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X40" s="92"/>
-    </row>
-    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="B41" s="145" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="150"/>
-      <c r="I41" s="151">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="152">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
-      <c r="M41" s="154"/>
-      <c r="N41" s="154"/>
-      <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
-      <c r="Q41" s="155"/>
-      <c r="R41" s="156">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="157">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T41" s="153"/>
-      <c r="U41" s="158">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V41" s="159">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="159">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X41" s="160"/>
-    </row>
-    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-      <c r="B42" s="162" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="165"/>
-      <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
-      <c r="H42" s="167"/>
-      <c r="I42" s="166">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="168">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
-      <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
-      <c r="Q42" s="170"/>
-      <c r="R42" s="171">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="172">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="169"/>
-      <c r="U42" s="173">
-        <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="174">
-        <f>U42/12</f>
-        <v>0</v>
-      </c>
-      <c r="W42" s="175">
-        <f>I42*12+J42</f>
-        <v>0</v>
-      </c>
-      <c r="X42" s="176"/>
-    </row>
-    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
-        <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="110"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="112"/>
-      <c r="F43" s="112"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="94">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="41"/>
-      <c r="L43" s="112"/>
-      <c r="M43" s="112"/>
-      <c r="N43" s="112"/>
-      <c r="O43" s="112"/>
-      <c r="P43" s="112"/>
-      <c r="Q43" s="120"/>
-      <c r="R43" s="161">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="127">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T43" s="41"/>
-      <c r="U43" s="107"/>
-      <c r="V43" s="109"/>
-      <c r="W43" s="129"/>
-      <c r="X43" s="27"/>
-    </row>
-    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="B44" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="115"/>
-      <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="79"/>
-      <c r="I44" s="73">
-        <f>C44+E44-G44</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="177">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
-      <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
-      <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
-      <c r="Q44" s="122"/>
-      <c r="R44" s="178">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="179">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T44" s="51"/>
-      <c r="U44" s="131">
-        <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
-      </c>
-      <c r="V44" s="130">
-        <f>U44/6</f>
-        <v>0</v>
-      </c>
-      <c r="W44" s="133">
-        <f>I44*6+J44</f>
-        <v>0</v>
-      </c>
-      <c r="X44" s="52"/>
-      <c r="Z44" s="47"/>
-    </row>
-    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="110"/>
-      <c r="D45" s="111"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="80">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="41"/>
-      <c r="L45" s="112"/>
-      <c r="M45" s="112"/>
-      <c r="N45" s="112"/>
-      <c r="O45" s="112"/>
-      <c r="P45" s="112"/>
-      <c r="Q45" s="120"/>
-      <c r="R45" s="96">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="127">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T45" s="41"/>
-      <c r="U45" s="107"/>
-      <c r="V45" s="132"/>
-      <c r="W45" s="129"/>
-      <c r="X45" s="27"/>
-    </row>
-    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="110"/>
-      <c r="D46" s="111"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="93">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="41"/>
-      <c r="L46" s="112"/>
-      <c r="M46" s="112"/>
-      <c r="N46" s="112"/>
-      <c r="O46" s="112"/>
-      <c r="P46" s="112"/>
-      <c r="Q46" s="120"/>
-      <c r="R46" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S46" s="128">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T46" s="41"/>
-      <c r="U46" s="107">
-        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="134">
-        <f t="shared" ref="V46:V47" si="12">U46/24</f>
-        <v>0</v>
-      </c>
-      <c r="W46" s="129">
-        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
-      </c>
-      <c r="X46" s="27"/>
-    </row>
-    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
-        <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="110"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="41"/>
-      <c r="L47" s="112"/>
-      <c r="M47" s="112"/>
-      <c r="N47" s="112"/>
-      <c r="O47" s="112"/>
-      <c r="P47" s="112"/>
-      <c r="Q47" s="120"/>
-      <c r="R47" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S47" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T47" s="41"/>
-      <c r="U47" s="107">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V47" s="130">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W47" s="129">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="X47" s="27"/>
-    </row>
-    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-      <c r="B48" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
-      <c r="E48" s="121"/>
-      <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
-      <c r="H48" s="139"/>
-      <c r="I48" s="139">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="140">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
-      <c r="P48" s="121"/>
-      <c r="Q48" s="122"/>
-      <c r="R48" s="97">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S48" s="144">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T48" s="51"/>
-      <c r="U48" s="131">
-        <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
-      </c>
-      <c r="V48" s="135">
-        <f>U48/6</f>
-        <v>0</v>
-      </c>
-      <c r="W48" s="133">
-        <f>I48*6+J48</f>
-        <v>0</v>
-      </c>
-      <c r="X48" s="52"/>
-    </row>
-    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
-        <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="110"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="41"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="112"/>
-      <c r="O49" s="112"/>
-      <c r="P49" s="112"/>
-      <c r="Q49" s="120"/>
-      <c r="R49" s="96">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="126">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T49" s="41"/>
-      <c r="U49" s="107">
-        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="109">
-        <f t="shared" ref="V49:V51" si="15">U49/24</f>
-        <v>0</v>
-      </c>
-      <c r="W49" s="129">
-        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
-      </c>
-      <c r="X49" s="27"/>
-    </row>
-    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
-        <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="110"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="41"/>
-      <c r="L50" s="112"/>
-      <c r="M50" s="112"/>
-      <c r="N50" s="112"/>
-      <c r="O50" s="112"/>
-      <c r="P50" s="112"/>
-      <c r="Q50" s="120"/>
-      <c r="R50" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T50" s="41"/>
-      <c r="U50" s="107">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="130">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W50" s="129">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="X50" s="27"/>
-    </row>
-    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="110"/>
-      <c r="D51" s="111"/>
-      <c r="E51" s="112"/>
-      <c r="F51" s="112"/>
-      <c r="G51" s="76"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="41"/>
-      <c r="L51" s="112"/>
-      <c r="M51" s="112"/>
-      <c r="N51" s="112"/>
-      <c r="O51" s="112"/>
-      <c r="P51" s="112"/>
-      <c r="Q51" s="120"/>
-      <c r="R51" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T51" s="41"/>
-      <c r="U51" s="107">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V51" s="130">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="129">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="X51" s="27"/>
-    </row>
-    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
-        <f t="shared" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="B52" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="141"/>
-      <c r="D52" s="142"/>
-      <c r="E52" s="121"/>
-      <c r="F52" s="121"/>
-      <c r="G52" s="143"/>
-      <c r="H52" s="139"/>
-      <c r="I52" s="139">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="140">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="51"/>
-      <c r="L52" s="121"/>
-      <c r="M52" s="121"/>
-      <c r="N52" s="121"/>
-      <c r="O52" s="121"/>
-      <c r="P52" s="121"/>
-      <c r="Q52" s="122"/>
-      <c r="R52" s="97">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="144">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T52" s="51"/>
-      <c r="U52" s="131">
-        <f>L52*6+N52*6+P52*6</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="135">
-        <f>U52/6</f>
-        <v>0</v>
-      </c>
-      <c r="W52" s="133">
-        <f>I52*6+J52</f>
-        <v>0</v>
-      </c>
-      <c r="X52" s="52"/>
-    </row>
-    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
-        <f t="shared" si="3"/>
-        <v>46</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" s="110"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="76"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="41"/>
-      <c r="L53" s="112"/>
-      <c r="M53" s="112"/>
-      <c r="N53" s="112"/>
-      <c r="O53" s="112"/>
-      <c r="P53" s="112"/>
-      <c r="Q53" s="120"/>
-      <c r="R53" s="96">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="126">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T53" s="41"/>
-      <c r="U53" s="107">
-        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
-        <v>0</v>
-      </c>
-      <c r="V53" s="109">
-        <f t="shared" ref="V53:V54" si="18">U53/24</f>
-        <v>0</v>
-      </c>
-      <c r="W53" s="129">
-        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
-      </c>
-      <c r="X53" s="27"/>
-    </row>
-    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
-        <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="110"/>
-      <c r="D54" s="111"/>
-      <c r="E54" s="112"/>
-      <c r="F54" s="112"/>
-      <c r="G54" s="76"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="41"/>
-      <c r="L54" s="112"/>
-      <c r="M54" s="112"/>
-      <c r="N54" s="112"/>
-      <c r="O54" s="112"/>
-      <c r="P54" s="112"/>
-      <c r="Q54" s="120"/>
-      <c r="R54" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T54" s="41"/>
-      <c r="U54" s="107">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="130">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="129">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="X54" s="27"/>
-    </row>
-    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="110"/>
-      <c r="D55" s="111"/>
-      <c r="E55" s="112"/>
-      <c r="F55" s="112"/>
-      <c r="G55" s="76"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="41"/>
-      <c r="L55" s="112"/>
-      <c r="M55" s="112"/>
-      <c r="N55" s="112"/>
-      <c r="O55" s="112"/>
-      <c r="P55" s="112"/>
-      <c r="Q55" s="120"/>
-      <c r="R55" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T55" s="41"/>
-      <c r="U55" s="107"/>
-      <c r="V55" s="130"/>
-      <c r="W55" s="129"/>
-      <c r="X55" s="27"/>
-    </row>
-    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="110"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="112"/>
-      <c r="F56" s="112"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="41"/>
-      <c r="L56" s="112"/>
-      <c r="M56" s="112"/>
-      <c r="N56" s="112"/>
-      <c r="O56" s="112"/>
-      <c r="P56" s="112"/>
-      <c r="Q56" s="120"/>
-      <c r="R56" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S56" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T56" s="41"/>
-      <c r="U56" s="107"/>
-      <c r="V56" s="130"/>
-      <c r="W56" s="129"/>
-      <c r="X56" s="27"/>
-    </row>
-    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="110"/>
-      <c r="D57" s="111"/>
-      <c r="E57" s="112"/>
-      <c r="F57" s="112"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="41"/>
-      <c r="L57" s="112"/>
-      <c r="M57" s="112"/>
-      <c r="N57" s="112"/>
-      <c r="O57" s="112"/>
-      <c r="P57" s="112"/>
-      <c r="Q57" s="120"/>
-      <c r="R57" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T57" s="41"/>
-      <c r="U57" s="107"/>
-      <c r="V57" s="130"/>
-      <c r="W57" s="129"/>
-      <c r="X57" s="27"/>
-    </row>
-    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3">
-        <f t="shared" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="110"/>
-      <c r="D58" s="111"/>
-      <c r="E58" s="112"/>
-      <c r="F58" s="112"/>
-      <c r="G58" s="76"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="41"/>
-      <c r="L58" s="112"/>
-      <c r="M58" s="112"/>
-      <c r="N58" s="112"/>
-      <c r="O58" s="112"/>
-      <c r="P58" s="112"/>
-      <c r="Q58" s="120"/>
-      <c r="R58" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T58" s="41"/>
-      <c r="U58" s="107"/>
-      <c r="V58" s="130"/>
-      <c r="W58" s="129"/>
-      <c r="X58" s="27"/>
-    </row>
-    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3">
-        <f t="shared" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="110"/>
-      <c r="D59" s="111"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="41"/>
-      <c r="L59" s="112"/>
-      <c r="M59" s="112"/>
-      <c r="N59" s="112"/>
-      <c r="O59" s="112"/>
-      <c r="P59" s="112"/>
-      <c r="Q59" s="120"/>
-      <c r="R59" s="86">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S59" s="124">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T59" s="41"/>
-      <c r="U59" s="107"/>
-      <c r="V59" s="130"/>
-      <c r="W59" s="129"/>
-      <c r="X59" s="27"/>
-    </row>
-    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="43">
-        <f>SUM(C8:C59)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="54">
-        <f>SUM(D8:D59)</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="44">
-        <f>SUM(E8:E59)</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="44"/>
-      <c r="G60" s="28">
-        <f>SUM(G8:G59)</f>
-        <v>0</v>
-      </c>
-      <c r="H60" s="56">
-        <f>SUM(H8:H59)</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="56">
-        <f>SUM(I8:I59)</f>
-        <v>0</v>
-      </c>
-      <c r="J60" s="45">
-        <f>SUM(J8:J59)</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="46"/>
-      <c r="L60" s="74">
-        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
-      </c>
-      <c r="M60" s="74">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="N60" s="74">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O60" s="74">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P60" s="74">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="75">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="R60" s="85">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S60" s="84">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="T60" s="46"/>
-      <c r="U60" s="43">
-        <f>SUM(U8:U59)</f>
-        <v>0</v>
-      </c>
-      <c r="V60" s="102">
-        <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
-        <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>340751</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B546202A-BD4F-49AF-9CB9-EFD2FC5FDBA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0112C311-CCCC-4296-9FF3-187D1036309B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="05,04" sheetId="120" r:id="rId5"/>
     <sheet name="05,05" sheetId="121" r:id="rId6"/>
     <sheet name="05,08" sheetId="123" r:id="rId7"/>
+    <sheet name="05,09" sheetId="124" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -28,6 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05,04'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -647,8 +649,94 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{CC2C7961-6969-47BE-B936-671866D799CE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{D22C1E8F-DE36-41B8-87BA-2B0DA636FEE0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{9C7DE1DD-274D-468A-A3FD-1ED86CCA9F01}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2226,7 +2314,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2789,6 +2877,15 @@
     <xf numFmtId="167" fontId="2" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3228,15 +3325,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3261,62 +3358,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5567,7 +5664,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5585,7 +5682,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5601,7 +5698,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5617,7 +5714,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5635,7 +5732,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5651,7 +5748,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6046,17 +6143,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46174</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6081,62 +6178,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9640,7 +9737,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9658,7 +9755,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9674,7 +9771,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9690,7 +9787,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9708,7 +9805,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9724,7 +9821,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10119,17 +10216,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46175</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10154,62 +10251,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13779,7 +13876,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13797,7 +13894,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13813,7 +13910,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13829,7 +13926,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13847,7 +13944,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13863,7 +13960,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14258,17 +14355,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46176</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14293,62 +14390,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17824,7 +17921,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17842,7 +17939,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17858,7 +17955,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17874,7 +17971,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17892,7 +17989,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17908,7 +18005,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18303,17 +18400,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46178</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18338,62 +18435,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21881,7 +21978,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21899,7 +21996,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21915,7 +22012,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21931,7 +22028,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21949,7 +22046,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21965,7 +22062,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22360,17 +22457,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46179</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22395,62 +22492,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25911,7 +26008,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25929,7 +26026,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25945,7 +26042,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25961,7 +26058,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25979,7 +26076,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25995,7 +26092,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26390,17 +26487,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46181</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26425,62 +26522,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="197" t="s">
+      <c r="C4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="199" t="s">
+      <c r="E4" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201" t="s">
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="203" t="s">
+      <c r="H4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="206" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="210"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="198"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="204"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -29932,7 +30029,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -29950,7 +30047,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -29966,7 +30063,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -29982,7 +30079,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30000,7 +30097,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30016,7 +30113,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30040,6 +30137,4066 @@
         <v>3</v>
       </c>
       <c r="D69" s="184"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EB28BF-6C46-4483-9101-264754BF15F2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="196">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="199" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="200" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="201" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="202" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="203"/>
+      <c r="G4" s="204" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="206" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="208" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="206" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="210" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="211"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="213"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="190" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="205"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>23</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>561</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>96</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2304</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>139</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>4</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>96</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>4</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3240</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>23</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>3</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112">
+        <v>2</v>
+      </c>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112">
+        <v>1</v>
+      </c>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>72</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>3</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>480</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3047</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>33</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3014</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>2</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>12</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>33</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>792</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>72336</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>124</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>124</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2977</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>43</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>9</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>7</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>216</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>816</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>53</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>3</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>288</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>74</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>10</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112">
+        <v>5</v>
+      </c>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1550</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3999</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>178</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>3821</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>20</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>50</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>178</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1068</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>178</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>22927</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>28</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>1</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>24</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>656</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <f>131</f>
+        <v>131</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>39</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>9</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>3</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>27</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>468</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>39</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>1104</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>34700</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1152</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>33548</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>339</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>323</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>490</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>1152</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>6912</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1152</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>201291</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2795</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2795</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16771</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>45404</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>131</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1432</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>43972</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>119</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>376</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>397</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>659</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1432</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>9960</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1432</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>330779</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="191" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="192"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="193"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="194" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="194"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="195"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="188" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="189"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0112C311-CCCC-4296-9FF3-187D1036309B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE904E-FA52-45A2-9540-27A9D21D53B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="05,05" sheetId="121" r:id="rId6"/>
     <sheet name="05,08" sheetId="123" r:id="rId7"/>
     <sheet name="05,09" sheetId="124" r:id="rId8"/>
+    <sheet name="05,10" sheetId="125" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -30,6 +31,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,05'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'05,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -735,8 +737,94 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{22DE4616-5F24-4E23-A55F-82F8B11E712B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{DEB914F2-90F1-4F66-9AC1-1165E89C5168}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{F87298E6-2A02-4F3F-8428-034E08560468}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2314,7 +2402,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2886,6 +2974,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3325,15 +3422,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3358,62 +3455,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5664,7 +5761,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5682,7 +5779,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5698,7 +5795,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5714,7 +5811,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5732,7 +5829,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5748,7 +5845,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6143,17 +6240,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46174</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6178,62 +6275,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9737,7 +9834,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9755,7 +9852,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9771,7 +9868,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9787,7 +9884,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9805,7 +9902,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9821,7 +9918,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10216,17 +10313,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46175</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10251,62 +10348,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13876,7 +13973,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13894,7 +13991,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13910,7 +14007,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13926,7 +14023,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13944,7 +14041,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13960,7 +14057,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14355,17 +14452,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46176</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14390,62 +14487,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17921,7 +18018,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17939,7 +18036,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17955,7 +18052,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17971,7 +18068,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17989,7 +18086,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18005,7 +18102,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18400,17 +18497,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46178</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18435,62 +18532,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21978,7 +22075,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21996,7 +22093,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22012,7 +22109,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22028,7 +22125,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22046,7 +22143,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22062,7 +22159,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22457,17 +22554,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46179</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22492,62 +22589,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26008,7 +26105,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26026,7 +26123,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26042,7 +26139,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26058,7 +26155,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26076,7 +26173,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26092,7 +26189,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26487,17 +26584,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46181</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26522,62 +26619,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30029,7 +30126,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30047,7 +30144,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30063,7 +30160,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30079,7 +30176,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30097,7 +30194,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30113,7 +30210,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30508,17 +30605,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="196">
+      <c r="P1" s="199">
         <v>46181</v>
       </c>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="198"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30543,62 +30640,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="202" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="203"/>
-      <c r="G4" s="204" t="s">
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="210" t="s">
+      <c r="L4" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="211"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="211"/>
-      <c r="U4" s="211"/>
-      <c r="V4" s="212"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="213"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="199"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="205"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34089,7 +34186,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="191" t="s">
+      <c r="G62" s="194" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34107,7 +34204,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="192"/>
+      <c r="G63" s="195"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34123,7 +34220,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="193"/>
+      <c r="G64" s="196"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34139,7 +34236,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="194" t="s">
+      <c r="G65" s="197" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34157,7 +34254,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="194"/>
+      <c r="G66" s="197"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34173,7 +34270,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="195"/>
+      <c r="G67" s="198"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34197,6 +34294,4039 @@
         <v>3</v>
       </c>
       <c r="D69" s="189"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A039FBA9-D099-42A2-AE80-DC4B3F80ADEE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="199">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="201"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="202" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="203" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="204" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="205" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="206"/>
+      <c r="G4" s="207" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="209" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="211" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="209" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="213" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="216"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="193" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="208"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="210"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>23</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76">
+        <v>2</v>
+      </c>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>21</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112">
+        <v>2</v>
+      </c>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>2</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>48</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>2</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>513</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>96</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2304</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>135</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>19</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>116</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>456</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>19</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>2784</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>20</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>20</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112">
+        <v>4</v>
+      </c>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>480</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>20</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3014</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>10</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3004</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>10</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>240</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>72096</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>124</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>124</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2977</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>34</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>6</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>672</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>50</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>288</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>64</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1550</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3821</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>29</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>3792</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>15</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>174</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>29</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>22753</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>27</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>656</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>92</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>9</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>83</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>8</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>108</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>9</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>996</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>33548</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>650</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>32898</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>312</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>338</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>650</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>3900</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>650</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>197391</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2795</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143">
+        <v>2</v>
+      </c>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2793</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121">
+        <v>2</v>
+      </c>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>12</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>2</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16759</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>43972</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>119</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>747</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>43225</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>119</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>346</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>401</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>747</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>5562</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>747</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>325217</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="194" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="195"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="196"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="197" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="197"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="198"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="191" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="192"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE904E-FA52-45A2-9540-27A9D21D53B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940B6BD4-7682-4095-BC57-25ED056FA5D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="05,08" sheetId="123" r:id="rId7"/>
     <sheet name="05,09" sheetId="124" r:id="rId8"/>
     <sheet name="05,10" sheetId="125" r:id="rId9"/>
+    <sheet name="05,11 " sheetId="126" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -32,6 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'05,10'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'05,11 '!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -107,6 +109,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{716ACC37-6F2E-471E-B5FB-7CB8AA42546F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{D5ACC47B-B854-47BF-9170-B0AE0203A23A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{9175664B-AD15-4695-B7FC-2EE3B5839317}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{6E07D93F-91B2-4222-BAB6-B47783799BE8}">
       <text>
         <r>
           <rPr>
@@ -824,7 +912,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2402,7 +2490,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2983,6 +3071,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3422,15 +3519,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="P1" s="202"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3455,62 +3552,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5761,7 +5858,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5779,7 +5876,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5795,7 +5892,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5811,7 +5908,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5829,7 +5926,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5845,7 +5942,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6186,6 +6283,4037 @@
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28B4951-6A36-4AD6-9558-72AD2AE159BE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="202">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="205" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="206" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="207" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="212" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="214" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="212" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="216" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="196" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>21</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>21</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>513</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>96</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2304</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>116</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>114</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>48</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>2</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>2736</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3004</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>17</v>
+      </c>
+      <c r="H13" s="79">
+        <v>24</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>2987</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-24</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>15</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>17</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>24</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>408</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>71664</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>124</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>5</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>119</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2857</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>28</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>2</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>624</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>50</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>288</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>64</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1550</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3792</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>161</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>3631</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>108</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>53</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>161</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>966</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>161</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>21787</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>27</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>26</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>26</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>624</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>83</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>11</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>132</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>11</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>864</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>32898</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>534</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>32364</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>265</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>269</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>534</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>3204</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>534</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>194187</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2793</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143">
+        <v>3</v>
+      </c>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2790</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121">
+        <v>3</v>
+      </c>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>18</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>3</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16741</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>43225</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>119</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>761</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>24</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>42464</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>95</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>393</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>368</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>761</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>5568</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>761</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>319625</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="197" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="198"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="199"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="200" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="200"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="201"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="194" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="195"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6240,17 +10368,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46174</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6275,62 +10403,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9834,7 +13962,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9852,7 +13980,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9868,7 +13996,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9884,7 +14012,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9902,7 +14030,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9918,7 +14046,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10313,17 +14441,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46175</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10348,62 +14476,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13973,7 +18101,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13991,7 +18119,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14007,7 +18135,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14023,7 +18151,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14041,7 +18169,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14057,7 +18185,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14452,17 +18580,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46176</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14487,62 +18615,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18018,7 +22146,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18036,7 +22164,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18052,7 +22180,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18068,7 +22196,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18086,7 +22214,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18102,7 +22230,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18497,17 +22625,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46178</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18532,62 +22660,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22075,7 +26203,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22093,7 +26221,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22109,7 +26237,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22125,7 +26253,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22143,7 +26271,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22159,7 +26287,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22554,17 +26682,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46179</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22589,62 +26717,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26105,7 +30233,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26123,7 +30251,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26139,7 +30267,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26155,7 +30283,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26173,7 +30301,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26189,7 +30317,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26584,17 +30712,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46181</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26619,62 +30747,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30126,7 +34254,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30144,7 +34272,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30160,7 +34288,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30176,7 +34304,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30194,7 +34322,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30210,7 +34338,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30605,17 +34733,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46181</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30640,62 +34768,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34186,7 +38314,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34204,7 +38332,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34220,7 +38348,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34236,7 +38364,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34254,7 +38382,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34270,7 +38398,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34665,17 +38793,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="199">
+      <c r="P1" s="202">
         <v>46181</v>
       </c>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="201"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="204"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34700,62 +38828,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="205" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="207" t="s">
+      <c r="F4" s="209"/>
+      <c r="G4" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="211" t="s">
+      <c r="I4" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="209" t="s">
+      <c r="J4" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="213" t="s">
+      <c r="L4" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="215"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="216"/>
+      <c r="M4" s="217"/>
+      <c r="N4" s="217"/>
+      <c r="O4" s="217"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="217"/>
+      <c r="R4" s="217"/>
+      <c r="S4" s="217"/>
+      <c r="T4" s="217"/>
+      <c r="U4" s="217"/>
+      <c r="V4" s="218"/>
+      <c r="W4" s="217"/>
+      <c r="X4" s="219"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="207"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="208"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="210"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="213"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38219,7 +42347,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="194" t="s">
+      <c r="G62" s="197" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38237,7 +42365,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="195"/>
+      <c r="G63" s="198"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38253,7 +42381,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="196"/>
+      <c r="G64" s="199"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38269,7 +42397,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="197" t="s">
+      <c r="G65" s="200" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38287,7 +42415,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="197"/>
+      <c r="G66" s="200"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38303,7 +42431,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="198"/>
+      <c r="G67" s="201"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940B6BD4-7682-4095-BC57-25ED056FA5D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0668D274-2970-499E-9B98-793A957C7CA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="05,09" sheetId="124" r:id="rId8"/>
     <sheet name="05,10" sheetId="125" r:id="rId9"/>
     <sheet name="05,11 " sheetId="126" r:id="rId10"/>
+    <sheet name="05,12  " sheetId="127" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -34,6 +35,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'05,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'05,11 '!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'05,12  '!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -195,6 +197,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{6E07D93F-91B2-4222-BAB6-B47783799BE8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{634565B5-7BF8-49C9-B443-C293BE338822}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{FDA8D116-2057-4DEE-B394-5FEA2DAF73BA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{DA985F77-06F2-49F8-B9DE-8D53F2944198}">
       <text>
         <r>
           <rPr>
@@ -912,7 +1000,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2490,7 +2578,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3080,6 +3168,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3519,15 +3616,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3552,62 +3649,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5858,7 +5955,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5876,7 +5973,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5892,7 +5989,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5908,7 +6005,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5926,7 +6023,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5942,7 +6039,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6337,17 +6434,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46181</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6372,62 +6469,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9889,7 +9986,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9907,7 +10004,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9923,7 +10020,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9939,7 +10036,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9957,7 +10054,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9973,7 +10070,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -9997,6 +10094,4038 @@
         <v>3</v>
       </c>
       <c r="D69" s="195"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2476624-73D9-418A-92EB-BF18B9B20931}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="205">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="209" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="211" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="215" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="217" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="215" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="219" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="199" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>21</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76">
+        <v>3</v>
+      </c>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>18</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112">
+        <v>3</v>
+      </c>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>3</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>72</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>441</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>96</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78">
+        <v>2</v>
+      </c>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>94</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121">
+        <v>1</v>
+      </c>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121">
+        <v>1</v>
+      </c>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>48</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>2</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2256</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>114</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>7</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>107</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>5</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>168</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>7</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>2568</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2986</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>22</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>2964</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>12</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>22</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>528</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>71136</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>119</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>119</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2857</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>26</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>1</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>600</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>50</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>288</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76">
+        <v>1</v>
+      </c>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112">
+        <v>1</v>
+      </c>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>64</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1550</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3631</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>171</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>3460</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>103</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>68</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>171</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1026</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>171</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>20761</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>1</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>72</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>13</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>8</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>5</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>156</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>13</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>708</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>32364</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>699</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>31665</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>422</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>277</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>699</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>4194</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>699</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>189992</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <f>2790</f>
+        <v>2790</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2790</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16741</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>42463</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>118</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>919</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>41544</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>118</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>551</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>368</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>919</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>6240</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>919</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>313384</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="200" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="201"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="202"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="203" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="203"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="204"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="197" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="198"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -10368,17 +14497,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46174</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10403,62 +14532,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13962,7 +18091,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13980,7 +18109,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13996,7 +18125,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14012,7 +18141,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14030,7 +18159,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14046,7 +18175,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14441,17 +18570,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46175</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14476,62 +18605,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18101,7 +22230,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18119,7 +22248,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18135,7 +22264,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18151,7 +22280,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18169,7 +22298,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18185,7 +22314,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18580,17 +22709,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46176</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18615,62 +22744,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22146,7 +26275,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22164,7 +26293,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22180,7 +26309,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22196,7 +26325,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22214,7 +26343,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22230,7 +26359,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22625,17 +26754,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46178</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22660,62 +26789,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26203,7 +30332,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26221,7 +30350,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26237,7 +30366,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26253,7 +30382,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26271,7 +30400,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26287,7 +30416,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26682,17 +30811,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46179</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26717,62 +30846,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30233,7 +34362,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30251,7 +34380,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30267,7 +34396,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30283,7 +34412,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30301,7 +34430,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30317,7 +34446,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30712,17 +34841,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46181</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30747,62 +34876,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34254,7 +38383,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34272,7 +38401,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34288,7 +38417,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34304,7 +38433,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34322,7 +38451,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34338,7 +38467,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34733,17 +38862,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46181</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34768,62 +38897,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38314,7 +42443,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38332,7 +42461,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38348,7 +42477,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38364,7 +42493,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38382,7 +42511,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38398,7 +42527,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -38793,17 +42922,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="202">
+      <c r="P1" s="205">
         <v>46181</v>
       </c>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="204"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="206"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
+      <c r="W1" s="206"/>
+      <c r="X1" s="207"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38828,62 +42957,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="209" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="209"/>
-      <c r="G4" s="210" t="s">
+      <c r="F4" s="212"/>
+      <c r="G4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="212" t="s">
+      <c r="J4" s="215" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="216" t="s">
+      <c r="L4" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="217"/>
-      <c r="Q4" s="217"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="217"/>
-      <c r="U4" s="217"/>
-      <c r="V4" s="218"/>
-      <c r="W4" s="217"/>
-      <c r="X4" s="219"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="220"/>
+      <c r="X4" s="222"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="205"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="207"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="213"/>
+      <c r="G5" s="214"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42347,7 +46476,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="197" t="s">
+      <c r="G62" s="200" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42365,7 +46494,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="198"/>
+      <c r="G63" s="201"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42381,7 +46510,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="199"/>
+      <c r="G64" s="202"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42397,7 +46526,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="200" t="s">
+      <c r="G65" s="203" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42415,7 +46544,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="200"/>
+      <c r="G66" s="203"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -42431,7 +46560,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="201"/>
+      <c r="G67" s="204"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0668D274-2970-499E-9B98-793A957C7CA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596A74F3-12BC-4F26-A07A-715BB4873F03}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="05,10" sheetId="125" r:id="rId9"/>
     <sheet name="05,11 " sheetId="126" r:id="rId10"/>
     <sheet name="05,12  " sheetId="127" r:id="rId11"/>
+    <sheet name="05,15" sheetId="128" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -36,6 +37,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'05,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'05,11 '!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'05,12  '!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'05,15'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -283,6 +285,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{DA985F77-06F2-49F8-B9DE-8D53F2944198}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{FE4DBCEA-B6D5-41D9-94AF-D34824C6C6CB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{CD8E6288-B673-44C1-9D80-5F4B4CB8291E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{5E26A17E-DB3C-47C8-9A77-1D115D916662}">
       <text>
         <r>
           <rPr>
@@ -1000,7 +1088,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2578,7 +2666,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3177,6 +3265,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3616,15 +3713,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205"/>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="P1" s="208"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3649,62 +3746,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5955,7 +6052,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5973,7 +6070,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5989,7 +6086,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6005,7 +6102,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6023,7 +6120,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6039,7 +6136,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6434,17 +6531,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46181</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6469,62 +6566,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9986,7 +10083,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10004,7 +10101,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10020,7 +10117,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10036,7 +10133,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10054,7 +10151,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10070,7 +10167,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10465,17 +10562,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46181</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10500,62 +10597,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14018,7 +14115,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14036,7 +14133,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14052,7 +14149,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14068,7 +14165,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14086,7 +14183,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14102,7 +14199,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14126,6 +14223,4042 @@
         <v>3</v>
       </c>
       <c r="D69" s="198"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFCCB86-9811-4A01-961C-58193094CAFF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="208">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="211" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="212" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="214" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="218" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="220" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="218" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="222" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="202" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>18</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>18</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f>I8*24+J8</f>
+        <v>441</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="2">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>94</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="3">C9-G9</f>
+        <v>94</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" ref="W8:W12" si="4">I9*24+J9</f>
+        <v>2256</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>107</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>12</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>288</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>12</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="4"/>
+        <v>2280</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="4"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2964</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>44</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="3"/>
+        <v>2920</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>9</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>12</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>44</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>1056</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>44</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>70080</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>119</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>2</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="3"/>
+        <v>117</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2809</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>25</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>5</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112">
+        <v>2</v>
+      </c>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>480</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>50</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>12</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>264</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>3</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>64</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1550</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3460</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>279</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="3"/>
+        <v>3181</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>111</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>6</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>162</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>279</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1674</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>279</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>19087</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>1</v>
+      </c>
+      <c r="D41" s="147">
+        <v>8</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>59</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>17</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>6</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>6</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>204</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>17</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>504</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <f>31665</f>
+        <v>31665</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1184</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>30481</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>322</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>379</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>483</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>1184</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>7104</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1184</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>182888</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2790</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="3"/>
+        <v>2790</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16741</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>41544</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>118</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1544</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>40000</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>118</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>452</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>403</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>689</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1544</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>10518</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1544</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>302866</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="203" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="204"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="205"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="206" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="206"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="207"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="200" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="201"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -14497,17 +18630,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46174</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14532,62 +18665,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18091,7 +22224,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18109,7 +22242,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18125,7 +22258,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18141,7 +22274,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18159,7 +22292,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18175,7 +22308,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18570,17 +22703,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46175</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18605,62 +22738,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22230,7 +26363,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22248,7 +26381,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22264,7 +26397,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22280,7 +26413,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22298,7 +26431,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22314,7 +26447,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22709,17 +26842,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46176</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22744,62 +26877,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26275,7 +30408,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26293,7 +30426,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26309,7 +30442,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26325,7 +30458,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26343,7 +30476,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26359,7 +30492,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26754,17 +30887,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46178</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26789,62 +30922,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30332,7 +34465,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30350,7 +34483,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30366,7 +34499,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30382,7 +34515,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30400,7 +34533,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30416,7 +34549,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30811,17 +34944,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46179</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30846,62 +34979,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34362,7 +38495,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34380,7 +38513,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34396,7 +38529,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34412,7 +38545,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34430,7 +38563,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34446,7 +38579,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34841,17 +38974,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46181</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34876,62 +39009,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38383,7 +42516,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38401,7 +42534,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38417,7 +42550,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38433,7 +42566,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38451,7 +42584,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38467,7 +42600,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -38862,17 +42995,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46181</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38897,62 +43030,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42443,7 +46576,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42461,7 +46594,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42477,7 +46610,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42493,7 +46626,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42511,7 +46644,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -42527,7 +46660,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -42922,17 +47055,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="205">
+      <c r="P1" s="208">
         <v>46181</v>
       </c>
-      <c r="Q1" s="206"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="206"/>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
-      <c r="W1" s="206"/>
-      <c r="X1" s="207"/>
+      <c r="Q1" s="209"/>
+      <c r="R1" s="209"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
+      <c r="W1" s="209"/>
+      <c r="X1" s="210"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -42957,62 +47090,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="211" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="212" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="212"/>
-      <c r="G4" s="213" t="s">
+      <c r="F4" s="215"/>
+      <c r="G4" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="215" t="s">
+      <c r="H4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="217" t="s">
+      <c r="I4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="215" t="s">
+      <c r="J4" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="219" t="s">
+      <c r="L4" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="220"/>
-      <c r="U4" s="220"/>
-      <c r="V4" s="221"/>
-      <c r="W4" s="220"/>
-      <c r="X4" s="222"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="223"/>
+      <c r="Q4" s="223"/>
+      <c r="R4" s="223"/>
+      <c r="S4" s="223"/>
+      <c r="T4" s="223"/>
+      <c r="U4" s="223"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223"/>
+      <c r="X4" s="225"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="214"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="221"/>
+      <c r="J5" s="219"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -46476,7 +50609,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="200" t="s">
+      <c r="G62" s="203" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -46494,7 +50627,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="201"/>
+      <c r="G63" s="204"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -46510,7 +50643,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="202"/>
+      <c r="G64" s="205"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -46526,7 +50659,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="203" t="s">
+      <c r="G65" s="206" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -46544,7 +50677,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="203"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -46560,7 +50693,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="204"/>
+      <c r="G67" s="207"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B040034A-5416-478C-8629-994D24B498B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAF0918-3700-4400-9F5F-7ABF6D28A651}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="05,17" sheetId="130" r:id="rId14"/>
     <sheet name="05,18" sheetId="131" r:id="rId15"/>
     <sheet name="05,19" sheetId="132" r:id="rId16"/>
+    <sheet name="05,22" sheetId="133" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -46,6 +47,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'05,17'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'05,18'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'05,19'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'05,22'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -723,6 +725,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{30C1B344-966E-42E5-9349-2BBE7A991E56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{376637C1-50BF-458C-8D47-C60A58F072AC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{0957F17C-081F-4FE8-AE0D-443FAA6C62DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{5053ACDC-4E82-4DE4-9735-6CFA7A88D0DA}">
       <text>
         <r>
           <rPr>
@@ -1440,7 +1528,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -3018,7 +3106,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3635,6 +3723,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4074,15 +4171,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="P1" s="214"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4107,62 +4204,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6413,7 +6510,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -6431,7 +6528,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -6447,7 +6544,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6463,7 +6560,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6481,7 +6578,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6497,7 +6594,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6892,17 +6989,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6927,62 +7024,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10444,7 +10541,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10462,7 +10559,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10478,7 +10575,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10494,7 +10591,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10512,7 +10609,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10528,7 +10625,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10923,17 +11020,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10958,62 +11055,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14476,7 +14573,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14494,7 +14591,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14510,7 +14607,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14526,7 +14623,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14544,7 +14641,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14560,7 +14657,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14955,17 +15052,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14990,62 +15087,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18512,7 +18609,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18530,7 +18627,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18546,7 +18643,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18562,7 +18659,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18580,7 +18677,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18596,7 +18693,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18991,17 +19088,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -19026,62 +19123,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22571,7 +22668,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22589,7 +22686,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22605,7 +22702,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22621,7 +22718,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22639,7 +22736,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22655,7 +22752,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -23050,17 +23147,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -23085,62 +23182,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26619,7 +26716,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26637,7 +26734,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26653,7 +26750,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26669,7 +26766,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26687,7 +26784,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26703,7 +26800,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -27098,17 +27195,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -27133,62 +27230,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30666,7 +30763,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30684,7 +30781,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30700,7 +30797,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30716,7 +30813,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30734,7 +30831,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30750,7 +30847,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -31145,17 +31242,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -31180,62 +31277,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34689,7 +34786,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34707,7 +34804,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34723,7 +34820,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34739,7 +34836,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34757,7 +34854,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34773,7 +34870,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34797,6 +34894,4067 @@
         <v>3</v>
       </c>
       <c r="D69" s="204"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60BB7340-1E0E-46B2-A428-8DD1E98E472C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="214">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="217" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="218" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="219" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="220" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="224" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="226" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="224" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="228" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="208" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>18</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>18</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>441</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>94</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>94</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2256</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>86</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>84</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>1</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>48</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>2</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>2016</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2796</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>26</v>
+      </c>
+      <c r="H13" s="79">
+        <v>36</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>2770</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-36</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>9</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>26</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>36</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>624</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>66444</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>100</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>5</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>95</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>5</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>2281</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110">
+        <v>3</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76">
+        <v>1</v>
+      </c>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112">
+        <v>1</v>
+      </c>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>41</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>41</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>989</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>10</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>216</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>2</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76">
+        <v>1</v>
+      </c>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112">
+        <v>1</v>
+      </c>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>55</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>12</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>11</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>1046</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>2864</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>86</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>2778</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>5</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>10</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>71</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>516</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>86</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>16669</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110">
+        <v>2</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>48</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>180</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>6</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>174</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154">
+        <v>5</v>
+      </c>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154">
+        <v>1</v>
+      </c>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>144</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>4196</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>362</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>70</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>56</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>1</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>13</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>70</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>840</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>70</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>3504</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>30593</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>926</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>29667</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>298</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>328</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>926</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>5556</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>926</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>178004</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110">
+        <v>8</v>
+      </c>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>192</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2787</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2787</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16723</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>40114</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>130</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1136</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>36</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>38978</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>94</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>392</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>351</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>393</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1136</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>36</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>8208</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1136</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>297274</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="209" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="210"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="211"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="212" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="212"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="213"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="206" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="207"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -35168,17 +39326,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46174</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -35203,62 +39361,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38762,7 +42920,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38780,7 +42938,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38796,7 +42954,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38812,7 +42970,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38830,7 +42988,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38846,7 +43004,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -39241,17 +43399,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46175</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -39276,62 +43434,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42901,7 +47059,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42919,7 +47077,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42935,7 +47093,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42951,7 +47109,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42969,7 +47127,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -42985,7 +47143,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -43380,17 +47538,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46176</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -43415,62 +47573,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -46946,7 +51104,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -46964,7 +51122,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -46980,7 +51138,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -46996,7 +51154,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -47014,7 +51172,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -47030,7 +51188,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -47425,17 +51583,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46178</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -47460,62 +51618,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -51003,7 +55161,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -51021,7 +55179,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -51037,7 +55195,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -51053,7 +55211,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -51071,7 +55229,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -51087,7 +55245,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -51482,17 +55640,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46179</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -51517,62 +55675,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -55033,7 +59191,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -55051,7 +59209,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -55067,7 +59225,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -55083,7 +59241,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -55101,7 +59259,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -55117,7 +59275,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -55512,17 +59670,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -55547,62 +59705,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -59054,7 +63212,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -59072,7 +63230,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -59088,7 +63246,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -59104,7 +63262,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -59122,7 +63280,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -59138,7 +63296,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -59533,17 +63691,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -59568,62 +63726,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -63114,7 +67272,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -63132,7 +67290,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -63148,7 +67306,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -63164,7 +67322,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -63182,7 +67340,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -63198,7 +67356,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -63593,17 +67751,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="211">
+      <c r="P1" s="214">
         <v>46181</v>
       </c>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="213"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="216"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -63628,62 +67786,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="216" t="s">
+      <c r="D4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="221"/>
+      <c r="G4" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="221" t="s">
+      <c r="H4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="223" t="s">
+      <c r="I4" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221" t="s">
+      <c r="J4" s="224" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="226"/>
-      <c r="N4" s="226"/>
-      <c r="O4" s="226"/>
-      <c r="P4" s="226"/>
-      <c r="Q4" s="226"/>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="227"/>
-      <c r="W4" s="226"/>
-      <c r="X4" s="228"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="229"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="230"/>
+      <c r="W4" s="229"/>
+      <c r="X4" s="231"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="219"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="220"/>
-      <c r="H5" s="222"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="222"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="225"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -67147,7 +71305,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="206" t="s">
+      <c r="G62" s="209" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -67165,7 +71323,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="207"/>
+      <c r="G63" s="210"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -67181,7 +71339,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="208"/>
+      <c r="G64" s="211"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -67197,7 +71355,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="209" t="s">
+      <c r="G65" s="212" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -67215,7 +71373,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="209"/>
+      <c r="G66" s="212"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -67231,7 +71389,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="210"/>
+      <c r="G67" s="213"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAF0918-3700-4400-9F5F-7ABF6D28A651}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E30FBB-DC15-49F0-9335-8156ECF781FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="05,18" sheetId="131" r:id="rId15"/>
     <sheet name="05,19" sheetId="132" r:id="rId16"/>
     <sheet name="05,22" sheetId="133" r:id="rId17"/>
+    <sheet name="05,23" sheetId="134" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -48,6 +49,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'05,18'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'05,19'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'05,22'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'05,23'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -839,6 +841,92 @@
 </comments>
 </file>
 
+<file path=xl/comments18.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{D8099D0A-D5C1-4463-B606-6F7014F84E71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{F4572DB7-0060-46AB-A9F3-21D8C6107D53}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{4AAE63AD-FBBA-4658-AD91-F66A97D8596B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1528,7 +1616,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -3106,7 +3194,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3732,6 +3820,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4171,15 +4268,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4204,62 +4301,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6510,7 +6607,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -6528,7 +6625,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -6544,7 +6641,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6560,7 +6657,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6578,7 +6675,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6594,7 +6691,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6989,17 +7086,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -7024,62 +7121,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10541,7 +10638,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10559,7 +10656,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10575,7 +10672,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10591,7 +10688,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10609,7 +10706,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10625,7 +10722,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -11020,17 +11117,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -11055,62 +11152,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14573,7 +14670,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14591,7 +14688,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14607,7 +14704,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14623,7 +14720,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14641,7 +14738,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14657,7 +14754,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -15052,17 +15149,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -15087,62 +15184,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18609,7 +18706,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18627,7 +18724,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18643,7 +18740,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18659,7 +18756,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18677,7 +18774,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18693,7 +18790,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -19088,17 +19185,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -19123,62 +19220,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22668,7 +22765,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22686,7 +22783,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22702,7 +22799,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22718,7 +22815,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22736,7 +22833,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22752,7 +22849,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -23147,17 +23244,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -23182,62 +23279,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26716,7 +26813,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26734,7 +26831,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26750,7 +26847,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26766,7 +26863,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26784,7 +26881,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26800,7 +26897,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -27195,17 +27292,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -27230,62 +27327,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30763,7 +30860,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30781,7 +30878,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30797,7 +30894,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30813,7 +30910,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30831,7 +30928,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30847,7 +30944,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -31242,17 +31339,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -31277,62 +31374,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34786,7 +34883,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34804,7 +34901,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34820,7 +34917,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34836,7 +34933,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34854,7 +34951,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34870,7 +34967,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -35265,17 +35362,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -35300,62 +35397,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38847,7 +38944,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38865,7 +38962,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38881,7 +38978,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38897,7 +38994,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38915,7 +39012,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38931,7 +39028,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -38955,6 +39052,4074 @@
         <v>3</v>
       </c>
       <c r="D69" s="207"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39769E8B-1E55-43B9-8348-1C697F8479F2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="217">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="220" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="221" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="222" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="223" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="227" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="229" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="227" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="231" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="211" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>18</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>17</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112">
+        <v>1</v>
+      </c>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>1</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>24</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>417</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>94</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>93</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121">
+        <v>1</v>
+      </c>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>24</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2232</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>84</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>84</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>2016</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2768</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>34</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>2734</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>12</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>8</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>34</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>816</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>65628</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>95</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>24</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>12</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>12</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>576</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>1705</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110">
+        <v>2</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>192</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>4608</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>41</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>5</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>869</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>9</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110">
+        <v>5</v>
+      </c>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>1</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>43</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>7</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>2</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>168</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>878</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <f>2778</f>
+        <v>2778</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>134</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>2644</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>6</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>20</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>134</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>804</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>134</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>15865</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110">
+        <v>2</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>48</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>174</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>10</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>164</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>240</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>3956</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>292</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>60</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>232</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>5</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>4</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>51</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>720</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>60</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>2784</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>29667</v>
+      </c>
+      <c r="D44" s="114">
+        <v>2</v>
+      </c>
+      <c r="E44" s="115">
+        <v>1512</v>
+      </c>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1272</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>29907</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>459</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>277</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>536</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>1272</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>7632</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1272</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>179444</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110">
+        <v>8</v>
+      </c>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>192</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2787</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143">
+        <v>5</v>
+      </c>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2782</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121">
+        <v>2</v>
+      </c>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>30</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>5</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16693</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>39173</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>142</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>1512</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1554</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>39131</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>142</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>495</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>309</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>750</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1554</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>11178</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1554</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>299896</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="212" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="213"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="214"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="215" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="215"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="216"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="209" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="210"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -39326,17 +43491,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46174</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -39361,62 +43526,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42920,7 +47085,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42938,7 +47103,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42954,7 +47119,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42970,7 +47135,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42988,7 +47153,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -43004,7 +47169,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -43399,17 +47564,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46175</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -43434,62 +47599,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -47059,7 +51224,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -47077,7 +51242,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -47093,7 +51258,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -47109,7 +51274,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -47127,7 +51292,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -47143,7 +51308,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -47538,17 +51703,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46176</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -47573,62 +51738,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -51104,7 +55269,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -51122,7 +55287,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -51138,7 +55303,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -51154,7 +55319,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -51172,7 +55337,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -51188,7 +55353,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -51583,17 +55748,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46178</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -51618,62 +55783,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -55161,7 +59326,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -55179,7 +59344,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -55195,7 +59360,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -55211,7 +59376,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -55229,7 +59394,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -55245,7 +59410,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -55640,17 +59805,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46179</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -55675,62 +59840,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -59191,7 +63356,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -59209,7 +63374,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -59225,7 +63390,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -59241,7 +63406,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -59259,7 +63424,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -59275,7 +63440,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -59670,17 +63835,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -59705,62 +63870,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -63212,7 +67377,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -63230,7 +67395,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -63246,7 +67411,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -63262,7 +67427,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -63280,7 +67445,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -63296,7 +67461,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -63691,17 +67856,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -63726,62 +67891,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -67272,7 +71437,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -67290,7 +71455,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -67306,7 +71471,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -67322,7 +71487,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -67340,7 +71505,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -67356,7 +71521,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -67751,17 +71916,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="214">
+      <c r="P1" s="217">
         <v>46181</v>
       </c>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="215"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="215"/>
-      <c r="V1" s="215"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="216"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="218"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="218"/>
+      <c r="V1" s="218"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="219"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -67786,62 +71951,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="220" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="220" t="s">
+      <c r="E4" s="223" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="221"/>
-      <c r="G4" s="222" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="224" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="226" t="s">
+      <c r="I4" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="224" t="s">
+      <c r="J4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="228" t="s">
+      <c r="L4" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="229"/>
-      <c r="U4" s="229"/>
-      <c r="V4" s="230"/>
-      <c r="W4" s="229"/>
-      <c r="X4" s="231"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="232"/>
+      <c r="T4" s="232"/>
+      <c r="U4" s="232"/>
+      <c r="V4" s="233"/>
+      <c r="W4" s="232"/>
+      <c r="X4" s="234"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="219"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="222"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="223"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="225"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="228"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -71305,7 +75470,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="209" t="s">
+      <c r="G62" s="212" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -71323,7 +75488,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="210"/>
+      <c r="G63" s="213"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -71339,7 +75504,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="211"/>
+      <c r="G64" s="214"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -71355,7 +75520,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="212" t="s">
+      <c r="G65" s="215" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -71373,7 +75538,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="212"/>
+      <c r="G66" s="215"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -71389,7 +75554,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="213"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/DSSR GBDS MONTH OF JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E30FBB-DC15-49F0-9335-8156ECF781FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D69B9C6-78B7-4E20-B2A2-D38CC1C36FF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="05,19" sheetId="132" r:id="rId16"/>
     <sheet name="05,22" sheetId="133" r:id="rId17"/>
     <sheet name="05,23" sheetId="134" r:id="rId18"/>
+    <sheet name="05,24" sheetId="135" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -50,6 +51,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'05,19'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'05,22'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'05,23'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'05,24'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -927,6 +929,92 @@
 </comments>
 </file>
 
+<file path=xl/comments19.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{A9FC904E-36F4-4A2B-841A-B02DC9F8CB89}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{D2B648FE-AC1D-44D5-A8F1-4B77E2D33425}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{D808F2B4-FE2A-4B52-AFE0-3DB815256B49}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1616,7 +1704,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -3194,7 +3282,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3829,6 +3917,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4268,15 +4365,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4301,62 +4398,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6607,7 +6704,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -6625,7 +6722,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -6641,7 +6738,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6657,7 +6754,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6675,7 +6772,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6691,7 +6788,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -7086,17 +7183,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -7121,62 +7218,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10638,7 +10735,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10656,7 +10753,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10672,7 +10769,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10688,7 +10785,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10706,7 +10803,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10722,7 +10819,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -11117,17 +11214,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -11152,62 +11249,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14670,7 +14767,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14688,7 +14785,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14704,7 +14801,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14720,7 +14817,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14738,7 +14835,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14754,7 +14851,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -15149,17 +15246,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -15184,62 +15281,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18706,7 +18803,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18724,7 +18821,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18740,7 +18837,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18756,7 +18853,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18774,7 +18871,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18790,7 +18887,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -19185,17 +19282,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -19220,62 +19317,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22765,7 +22862,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22783,7 +22880,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22799,7 +22896,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22815,7 +22912,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22833,7 +22930,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22849,7 +22946,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -23244,17 +23341,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -23279,62 +23376,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26813,7 +26910,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26831,7 +26928,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26847,7 +26944,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26863,7 +26960,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26881,7 +26978,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26897,7 +26994,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -27292,17 +27389,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -27327,62 +27424,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30860,7 +30957,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30878,7 +30975,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30894,7 +30991,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30910,7 +31007,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30928,7 +31025,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30944,7 +31041,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -31339,17 +31436,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -31374,62 +31471,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34883,7 +34980,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34901,7 +34998,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34917,7 +35014,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34933,7 +35030,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34951,7 +35048,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34967,7 +35064,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -35362,17 +35459,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -35397,62 +35494,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38944,7 +39041,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38962,7 +39059,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38978,7 +39075,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38994,7 +39091,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -39012,7 +39109,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -39028,7 +39125,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -39423,17 +39520,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -39458,62 +39555,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="211" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -43012,7 +43109,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -43030,7 +43127,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -43046,7 +43143,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -43062,7 +43159,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -43080,7 +43177,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -43096,7 +43193,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -43120,6 +43217,4081 @@
         <v>3</v>
       </c>
       <c r="D69" s="210"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185D7E18-409A-43A4-B588-AB5C63C0050E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="220">
+        <v>46181</v>
+      </c>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="223" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="224" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="225" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="226" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="230" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="232" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="230" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="234" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="214" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>17</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>17</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>417</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>93</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>93</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2232</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>84</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>6</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>78</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>5</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>144</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>6</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>1872</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>122</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>2734</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>29</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>2705</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>2</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>11</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>29</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>696</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>64920</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>71</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>1</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>1681</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110">
+        <v>2</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76">
+        <v>1</v>
+      </c>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112">
+        <v>1</v>
+      </c>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>192</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>4608</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>36</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>3</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>797</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>8</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>2</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112">
+        <v>1</v>
+      </c>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>144</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110">
+        <v>5</v>
+      </c>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>1</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76">
+        <v>1</v>
+      </c>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112">
+        <v>1</v>
+      </c>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>36</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>854</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>2644</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>68</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>2576</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>43</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>5</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>68</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>408</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>68</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>15457</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110">
+        <v>2</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76">
+        <v>1</v>
+      </c>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112">
+        <v>1</v>
+      </c>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>24</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>24</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>164</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>164</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>3956</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>232</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>30</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>5</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>360</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>30</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>2424</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>29907</v>
+      </c>
+      <c r="D44" s="114">
+        <v>1</v>
+      </c>
+      <c r="E44" s="115">
+        <v>3672</v>
+      </c>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1215</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>32364</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>315</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>327</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>513</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>1155</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>6930</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1155</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>194185</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110">
+        <v>8</v>
+      </c>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76">
+        <v>1</v>
+      </c>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112">
+        <v>1</v>
+      </c>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>24</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>1</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>168</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2782</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2782</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16693</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>39131</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>141</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>3672</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1359</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>41444</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>129</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>378</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>347</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>574</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1299</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>8802</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1299</v>
+      </c>
+      <c r="W60" s="187">
+        <f>SUM(W8:W59)</f>
+        <v>312753</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="215" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="216"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="217"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="218" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="218"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="219"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="212" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="213"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -43491,17 +47663,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46174</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -43526,62 +47698,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -47085,7 +51257,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -47103,7 +51275,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -47119,7 +51291,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -47135,7 +51307,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -47153,7 +51325,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -47169,7 +51341,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -47564,17 +51736,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46175</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -47599,62 +51771,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -51224,7 +55396,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -51242,7 +55414,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -51258,7 +55430,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -51274,7 +55446,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -51292,7 +55464,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -51308,7 +55480,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -51703,17 +55875,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46176</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -51738,62 +55910,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -55269,7 +59441,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -55287,7 +59459,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -55303,7 +59475,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -55319,7 +59491,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -55337,7 +59509,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -55353,7 +59525,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -55748,17 +59920,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46178</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -55783,62 +59955,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -59326,7 +63498,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -59344,7 +63516,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -59360,7 +63532,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -59376,7 +63548,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -59394,7 +63566,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -59410,7 +63582,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -59805,17 +63977,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46179</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -59840,62 +64012,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -63356,7 +67528,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -63374,7 +67546,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -63390,7 +67562,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -63406,7 +67578,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -63424,7 +67596,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -63440,7 +67612,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -63835,17 +68007,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -63870,62 +68042,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -67377,7 +71549,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -67395,7 +71567,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -67411,7 +71583,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -67427,7 +71599,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -67445,7 +71617,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -67461,7 +71633,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -67856,17 +72028,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -67891,62 +72063,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -71437,7 +75609,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -71455,7 +75627,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -71471,7 +75643,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -71487,7 +75659,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -71505,7 +75677,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -71521,7 +75693,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -71916,17 +76088,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="217">
+      <c r="P1" s="220">
         <v>46181</v>
       </c>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="218"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="218"/>
-      <c r="V1" s="218"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="219"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="221"/>
+      <c r="S1" s="221"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="222"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -71951,62 +76123,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="221" t="s">
+      <c r="C4" s="224" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="223" t="s">
+      <c r="E4" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="224"/>
-      <c r="G4" s="225" t="s">
+      <c r="F4" s="227"/>
+      <c r="G4" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="227" t="s">
+      <c r="H4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="229" t="s">
+      <c r="I4" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="227" t="s">
+      <c r="J4" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="231" t="s">
+      <c r="L4" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="232"/>
-      <c r="N4" s="232"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="232"/>
-      <c r="T4" s="232"/>
-      <c r="U4" s="232"/>
-      <c r="V4" s="233"/>
-      <c r="W4" s="232"/>
-      <c r="X4" s="234"/>
+      <c r="M4" s="235"/>
+      <c r="N4" s="235"/>
+      <c r="O4" s="235"/>
+      <c r="P4" s="235"/>
+      <c r="Q4" s="235"/>
+      <c r="R4" s="235"/>
+      <c r="S4" s="235"/>
+      <c r="T4" s="235"/>
+      <c r="U4" s="235"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="235"/>
+      <c r="X4" s="237"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="225"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="226"/>
-      <c r="H5" s="228"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="228"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="231"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -75470,7 +79642,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="212" t="s">
+      <c r="G62" s="215" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -75488,7 +79660,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="213"/>
+      <c r="G63" s="216"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -75504,7 +79676,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="214"/>
+      <c r="G64" s="217"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -75520,7 +79692,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="215" t="s">
+      <c r="G65" s="218" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -75538,7 +79710,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="215"/>
+      <c r="G66" s="218"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -75554,7 +79726,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="216"/>
+      <c r="G67" s="219"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
